--- a/research/traditional_assets/database/data/switzerland/switzerland_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_furn_home_furnishings.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0862625295078759</v>
+        <v>0.08617501621479438</v>
       </c>
       <c r="C2">
-        <v>377.1985789144888</v>
+        <v>374.0795636934012</v>
       </c>
       <c r="D2">
-        <v>326.6985789144888</v>
+        <v>327.4067016885766</v>
       </c>
       <c r="E2">
-        <v>-34.41379951754185</v>
+        <v>-30.58666152236643</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.827137995175419</v>
       </c>
       <c r="G2">
         <v>50.5</v>
@@ -1433,28 +1433,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1925050411573236</v>
       </c>
       <c r="N2">
-        <v>36.90000000000001</v>
+        <v>36.70749495884268</v>
       </c>
       <c r="O2">
-        <v>5.3874</v>
+        <v>5.359294263991031</v>
       </c>
       <c r="P2">
-        <v>31.51260000000001</v>
+        <v>31.34820069485165</v>
       </c>
       <c r="Q2">
-        <v>65.1126</v>
+        <v>64.94820069485164</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0862625295078759</v>
+        <v>0.08661156991393373</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460946</v>
+        <v>0.942530483000779</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>191.6832919188007</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08617501621479438</v>
+        <v>0.0860875029217129</v>
       </c>
       <c r="C3">
-        <v>374.0795636934012</v>
+        <v>370.9636248682859</v>
       </c>
       <c r="D3">
-        <v>327.4067016885766</v>
+        <v>328.1179008586367</v>
       </c>
       <c r="E3">
-        <v>-30.58666152236643</v>
+        <v>-26.75952352719101</v>
       </c>
       <c r="F3">
-        <v>3.827137995175419</v>
+        <v>7.654275990350838</v>
       </c>
       <c r="G3">
         <v>50.5</v>
@@ -1515,28 +1515,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M3">
-        <v>0.1925050411573236</v>
+        <v>0.3850100823146471</v>
       </c>
       <c r="N3">
-        <v>36.70749495884268</v>
+        <v>36.51498991768536</v>
       </c>
       <c r="O3">
-        <v>5.359294263991031</v>
+        <v>5.331188527982062</v>
       </c>
       <c r="P3">
-        <v>31.34820069485165</v>
+        <v>31.18380138970329</v>
       </c>
       <c r="Q3">
-        <v>64.94820069485164</v>
+        <v>64.78380138970329</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08661156991393373</v>
+        <v>0.08696773359358459</v>
       </c>
       <c r="T3">
-        <v>0.942530483000779</v>
+        <v>0.9507559721382122</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.6832919188007</v>
+        <v>95.84164595940037</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0860875029217129</v>
+        <v>0.08599998962863138</v>
       </c>
       <c r="C4">
-        <v>370.9636248682859</v>
+        <v>367.8507825306069</v>
       </c>
       <c r="D4">
-        <v>328.1179008586367</v>
+        <v>328.8321965161331</v>
       </c>
       <c r="E4">
-        <v>-26.75952352719101</v>
+        <v>-22.93238553201559</v>
       </c>
       <c r="F4">
-        <v>7.654275990350838</v>
+        <v>11.48141398552626</v>
       </c>
       <c r="G4">
         <v>50.5</v>
@@ -1597,28 +1597,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M4">
-        <v>0.3850100823146471</v>
+        <v>0.5775151234719706</v>
       </c>
       <c r="N4">
-        <v>36.51498991768536</v>
+        <v>36.32248487652804</v>
       </c>
       <c r="O4">
-        <v>5.331188527982062</v>
+        <v>5.303082791973093</v>
       </c>
       <c r="P4">
-        <v>31.18380138970329</v>
+        <v>31.01940208455494</v>
       </c>
       <c r="Q4">
-        <v>64.78380138970329</v>
+        <v>64.61940208455493</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08696773359358459</v>
+        <v>0.08733124085425917</v>
       </c>
       <c r="T4">
-        <v>0.9507559721382122</v>
+        <v>0.9591510589898192</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.84164595940037</v>
+        <v>63.89443063960026</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08599998962863138</v>
+        <v>0.08591247633554991</v>
       </c>
       <c r="C5">
-        <v>367.8507825306069</v>
+        <v>364.7410569471613</v>
       </c>
       <c r="D5">
-        <v>328.8321965161331</v>
+        <v>329.5496089278629</v>
       </c>
       <c r="E5">
-        <v>-22.93238553201559</v>
+        <v>-19.10524753684017</v>
       </c>
       <c r="F5">
-        <v>11.48141398552626</v>
+        <v>15.30855198070168</v>
       </c>
       <c r="G5">
         <v>50.5</v>
@@ -1679,28 +1679,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M5">
-        <v>0.5775151234719706</v>
+        <v>0.7700201646292942</v>
       </c>
       <c r="N5">
-        <v>36.32248487652804</v>
+        <v>36.12997983537071</v>
       </c>
       <c r="O5">
-        <v>5.303082791973093</v>
+        <v>5.274977055964124</v>
       </c>
       <c r="P5">
-        <v>31.01940208455494</v>
+        <v>30.85500277940659</v>
       </c>
       <c r="Q5">
-        <v>64.61940208455493</v>
+        <v>64.45500277940658</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08733124085425917</v>
+        <v>0.08770232118286449</v>
       </c>
       <c r="T5">
-        <v>0.9591510589898192</v>
+        <v>0.9677210434841681</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.89443063960026</v>
+        <v>47.92082297970019</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08591247633554991</v>
+        <v>0.08582496304246841</v>
       </c>
       <c r="C6">
-        <v>364.7410569471613</v>
+        <v>361.6344685619979</v>
       </c>
       <c r="D6">
-        <v>329.5496089278629</v>
+        <v>330.270158537875</v>
       </c>
       <c r="E6">
-        <v>-19.10524753684017</v>
+        <v>-15.27810954166475</v>
       </c>
       <c r="F6">
-        <v>15.30855198070168</v>
+        <v>19.1356899758771</v>
       </c>
       <c r="G6">
         <v>50.5</v>
@@ -1761,28 +1761,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M6">
-        <v>0.7700201646292942</v>
+        <v>0.9625252057866178</v>
       </c>
       <c r="N6">
-        <v>36.12997983537071</v>
+        <v>35.93747479421339</v>
       </c>
       <c r="O6">
-        <v>5.274977055964124</v>
+        <v>5.246871319955154</v>
       </c>
       <c r="P6">
-        <v>30.85500277940659</v>
+        <v>30.69060347425823</v>
       </c>
       <c r="Q6">
-        <v>64.45500277940658</v>
+        <v>64.29060347425823</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08770232118286449</v>
+        <v>0.08808121372891412</v>
       </c>
       <c r="T6">
-        <v>0.9677210434841681</v>
+        <v>0.9764714487047138</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.92082297970019</v>
+        <v>38.33665838376015</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08582496304246841</v>
+        <v>0.08573744974938691</v>
       </c>
       <c r="C7">
-        <v>361.6344685619979</v>
+        <v>358.5310379983578</v>
       </c>
       <c r="D7">
-        <v>330.270158537875</v>
+        <v>330.9938659694103</v>
       </c>
       <c r="E7">
-        <v>-15.27810954166475</v>
+        <v>-11.45097154648933</v>
       </c>
       <c r="F7">
-        <v>19.1356899758771</v>
+        <v>22.96282797105252</v>
       </c>
       <c r="G7">
         <v>50.5</v>
@@ -1843,28 +1843,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M7">
-        <v>0.9625252057866178</v>
+        <v>1.155030246943942</v>
       </c>
       <c r="N7">
-        <v>35.93747479421339</v>
+        <v>35.74496975305606</v>
       </c>
       <c r="O7">
-        <v>5.246871319955154</v>
+        <v>5.218765583946185</v>
       </c>
       <c r="P7">
-        <v>30.69060347425823</v>
+        <v>30.52620416910987</v>
       </c>
       <c r="Q7">
-        <v>64.29060347425823</v>
+        <v>64.12620416910987</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08808121372891412</v>
+        <v>0.08846816781849672</v>
       </c>
       <c r="T7">
-        <v>0.9764714487047138</v>
+        <v>0.9854080327597392</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.33665838376015</v>
+        <v>31.94721531980012</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08573744974938691</v>
+        <v>0.08564993645630542</v>
       </c>
       <c r="C8">
-        <v>358.5310379983578</v>
+        <v>355.4307860606423</v>
       </c>
       <c r="D8">
-        <v>330.9938659694103</v>
+        <v>331.7207520268703</v>
       </c>
       <c r="E8">
-        <v>-11.45097154648933</v>
+        <v>-7.623833551313918</v>
       </c>
       <c r="F8">
-        <v>22.96282797105251</v>
+        <v>26.78996596622793</v>
       </c>
       <c r="G8">
         <v>50.5</v>
@@ -1925,28 +1925,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M8">
-        <v>1.155030246943941</v>
+        <v>1.347535288101265</v>
       </c>
       <c r="N8">
-        <v>35.74496975305606</v>
+        <v>35.55246471189874</v>
       </c>
       <c r="O8">
-        <v>5.218765583946185</v>
+        <v>5.190659847937217</v>
       </c>
       <c r="P8">
-        <v>30.52620416910987</v>
+        <v>30.36180486396153</v>
       </c>
       <c r="Q8">
-        <v>64.12620416910987</v>
+        <v>63.96180486396152</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08846816781849672</v>
+        <v>0.08886344350140367</v>
       </c>
       <c r="T8">
-        <v>0.9854080327597392</v>
+        <v>0.9945368014180984</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.94721531980013</v>
+        <v>27.38332741697154</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08564993645630541</v>
+        <v>0.08556242316322392</v>
       </c>
       <c r="C9">
-        <v>355.4307860606424</v>
+        <v>352.3337337364075</v>
       </c>
       <c r="D9">
-        <v>331.7207520268704</v>
+        <v>332.4508376978109</v>
       </c>
       <c r="E9">
-        <v>-7.623833551313915</v>
+        <v>-3.796695556138495</v>
       </c>
       <c r="F9">
-        <v>26.78996596622793</v>
+        <v>30.61710396140335</v>
       </c>
       <c r="G9">
         <v>50.5</v>
@@ -2007,28 +2007,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M9">
-        <v>1.347535288101265</v>
+        <v>1.540040329258588</v>
       </c>
       <c r="N9">
-        <v>35.55246471189874</v>
+        <v>35.35995967074142</v>
       </c>
       <c r="O9">
-        <v>5.190659847937217</v>
+        <v>5.162554111928246</v>
       </c>
       <c r="P9">
-        <v>30.36180486396153</v>
+        <v>30.19740555881317</v>
       </c>
       <c r="Q9">
-        <v>63.96180486396152</v>
+        <v>63.79740555881317</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08886344350140367</v>
+        <v>0.08926731213393904</v>
       </c>
       <c r="T9">
-        <v>0.9945368014180984</v>
+        <v>1.003864021569031</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.38332741697154</v>
+        <v>23.9604114898501</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08556242316322392</v>
+        <v>0.08547490987014242</v>
       </c>
       <c r="C10">
-        <v>352.3337337364075</v>
+        <v>349.2399021983825</v>
       </c>
       <c r="D10">
-        <v>332.4508376978109</v>
+        <v>333.1841441549613</v>
       </c>
       <c r="E10">
-        <v>-3.796695556138495</v>
+        <v>0.03044243903691779</v>
       </c>
       <c r="F10">
-        <v>30.61710396140335</v>
+        <v>34.44424195657876</v>
       </c>
       <c r="G10">
         <v>50.5</v>
@@ -2089,28 +2089,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M10">
-        <v>1.540040329258588</v>
+        <v>1.732545370415912</v>
       </c>
       <c r="N10">
-        <v>35.35995967074142</v>
+        <v>35.16745462958409</v>
       </c>
       <c r="O10">
-        <v>5.162554111928246</v>
+        <v>5.134448375919277</v>
       </c>
       <c r="P10">
-        <v>30.19740555881317</v>
+        <v>30.03300625366482</v>
       </c>
       <c r="Q10">
-        <v>63.79740555881317</v>
+        <v>63.63300625366481</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08926731213393904</v>
+        <v>0.08968005700015649</v>
       </c>
       <c r="T10">
-        <v>1.003864021569031</v>
+        <v>1.013396235569434</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.9604114898501</v>
+        <v>21.29814354653342</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08547490987014242</v>
+        <v>0.0853873965770609</v>
       </c>
       <c r="C11">
-        <v>349.2399021983825</v>
+        <v>346.149312806518</v>
       </c>
       <c r="D11">
-        <v>333.1841441549613</v>
+        <v>333.9206927582721</v>
       </c>
       <c r="E11">
-        <v>0.03044243903691779</v>
+        <v>3.857580434212338</v>
       </c>
       <c r="F11">
-        <v>34.44424195657876</v>
+        <v>38.27137995175418</v>
       </c>
       <c r="G11">
         <v>50.5</v>
@@ -2171,28 +2171,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M11">
-        <v>1.732545370415912</v>
+        <v>1.925050411573235</v>
       </c>
       <c r="N11">
-        <v>35.16745462958409</v>
+        <v>34.97494958842677</v>
       </c>
       <c r="O11">
-        <v>5.134448375919277</v>
+        <v>5.106342639910308</v>
       </c>
       <c r="P11">
-        <v>30.03300625366482</v>
+        <v>29.86860694851646</v>
       </c>
       <c r="Q11">
-        <v>63.63300625366481</v>
+        <v>63.46860694851645</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08968005700015649</v>
+        <v>0.09010197397451211</v>
       </c>
       <c r="T11">
-        <v>1.013396235569434</v>
+        <v>1.023140276547624</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.29814354653342</v>
+        <v>19.16832919188008</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0853873965770609</v>
+        <v>0.08529988328397942</v>
       </c>
       <c r="C12">
-        <v>346.149312806518</v>
+        <v>343.0619871100585</v>
       </c>
       <c r="D12">
-        <v>333.9206927582721</v>
+        <v>334.660505056988</v>
       </c>
       <c r="E12">
-        <v>3.857580434212345</v>
+        <v>7.684718429387758</v>
       </c>
       <c r="F12">
-        <v>38.27137995175419</v>
+        <v>42.0985179469296</v>
       </c>
       <c r="G12">
         <v>50.5</v>
@@ -2253,28 +2253,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M12">
-        <v>1.925050411573236</v>
+        <v>2.117555452730559</v>
       </c>
       <c r="N12">
-        <v>34.97494958842677</v>
+        <v>34.78244454726945</v>
       </c>
       <c r="O12">
-        <v>5.106342639910308</v>
+        <v>5.078236903901339</v>
       </c>
       <c r="P12">
-        <v>29.86860694851646</v>
+        <v>29.70420764336811</v>
       </c>
       <c r="Q12">
-        <v>63.46860694851645</v>
+        <v>63.3042076433681</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09010197397451211</v>
+        <v>0.09053337222919036</v>
       </c>
       <c r="T12">
-        <v>1.023140276547624</v>
+        <v>1.033103284738807</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.16832919188007</v>
+        <v>17.42575381080007</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08529988328397942</v>
+        <v>0.08521236999089792</v>
       </c>
       <c r="C13">
-        <v>343.0619871100585</v>
+        <v>339.9779468496454</v>
       </c>
       <c r="D13">
-        <v>334.660505056988</v>
+        <v>335.4036027917505</v>
       </c>
       <c r="E13">
-        <v>7.684718429387758</v>
+        <v>11.51185642456318</v>
       </c>
       <c r="F13">
-        <v>42.0985179469296</v>
+        <v>45.92565594210502</v>
       </c>
       <c r="G13">
         <v>50.5</v>
@@ -2335,28 +2335,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M13">
-        <v>2.117555452730559</v>
+        <v>2.310060493887883</v>
       </c>
       <c r="N13">
-        <v>34.78244454726945</v>
+        <v>34.58993950611212</v>
       </c>
       <c r="O13">
-        <v>5.078236903901339</v>
+        <v>5.05013116789237</v>
       </c>
       <c r="P13">
-        <v>29.70420764336811</v>
+        <v>29.53980833821975</v>
       </c>
       <c r="Q13">
-        <v>63.3042076433681</v>
+        <v>63.13980833821975</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09053337222919036</v>
+        <v>0.09097457498965672</v>
       </c>
       <c r="T13">
-        <v>1.033103284738807</v>
+        <v>1.043292724934335</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.42575381080007</v>
+        <v>15.97360765990006</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08521236999089792</v>
+        <v>0.08512485669781641</v>
       </c>
       <c r="C14">
-        <v>339.9779468496454</v>
+        <v>336.8972139594462</v>
       </c>
       <c r="D14">
-        <v>335.4036027917505</v>
+        <v>336.1500078967266</v>
       </c>
       <c r="E14">
-        <v>11.51185642456318</v>
+        <v>15.3389944197386</v>
       </c>
       <c r="F14">
-        <v>45.92565594210502</v>
+        <v>49.75279393728044</v>
       </c>
       <c r="G14">
         <v>50.5</v>
@@ -2417,28 +2417,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M14">
-        <v>2.310060493887883</v>
+        <v>2.502565535045206</v>
       </c>
       <c r="N14">
-        <v>34.58993950611212</v>
+        <v>34.3974344649548</v>
       </c>
       <c r="O14">
-        <v>5.05013116789237</v>
+        <v>5.0220254318834</v>
       </c>
       <c r="P14">
-        <v>29.53980833821975</v>
+        <v>29.3754090330714</v>
       </c>
       <c r="Q14">
-        <v>63.13980833821975</v>
+        <v>62.97540903307139</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09097457498965672</v>
+        <v>0.09142592034231772</v>
       </c>
       <c r="T14">
-        <v>1.043292724934335</v>
+        <v>1.053716405134358</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.97360765990006</v>
+        <v>14.74486860913852</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08512485669781641</v>
+        <v>0.08503734340473493</v>
       </c>
       <c r="C15">
-        <v>336.8972139594462</v>
+        <v>333.8198105693118</v>
       </c>
       <c r="D15">
-        <v>336.1500078967266</v>
+        <v>336.8997425017676</v>
       </c>
       <c r="E15">
-        <v>15.3389944197386</v>
+        <v>19.16613241491402</v>
       </c>
       <c r="F15">
-        <v>49.75279393728044</v>
+        <v>53.57993193245586</v>
       </c>
       <c r="G15">
         <v>50.5</v>
@@ -2499,28 +2499,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M15">
-        <v>2.502565535045206</v>
+        <v>2.69507057620253</v>
       </c>
       <c r="N15">
-        <v>34.3974344649548</v>
+        <v>34.20492942379747</v>
       </c>
       <c r="O15">
-        <v>5.0220254318834</v>
+        <v>4.993919695874431</v>
       </c>
       <c r="P15">
-        <v>29.3754090330714</v>
+        <v>29.21100972792304</v>
       </c>
       <c r="Q15">
-        <v>62.97540903307139</v>
+        <v>62.81100972792304</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09142592034231772</v>
+        <v>0.09188776209852897</v>
       </c>
       <c r="T15">
-        <v>1.053716405134358</v>
+        <v>1.064382496501824</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.74486860913852</v>
+        <v>13.69166370848577</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08503734340473493</v>
+        <v>0.08514198011165343</v>
       </c>
       <c r="C16">
-        <v>333.8198105693118</v>
+        <v>329.0966302418229</v>
       </c>
       <c r="D16">
-        <v>336.8997425017676</v>
+        <v>336.0037001694542</v>
       </c>
       <c r="E16">
-        <v>19.16613241491402</v>
+        <v>22.99327041008944</v>
       </c>
       <c r="F16">
-        <v>53.57993193245586</v>
+        <v>57.40706992763129</v>
       </c>
       <c r="G16">
         <v>50.5</v>
@@ -2581,45 +2581,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M16">
-        <v>2.69507057620253</v>
+        <v>2.973686222251301</v>
       </c>
       <c r="N16">
-        <v>34.20492942379747</v>
+        <v>33.9263137777487</v>
       </c>
       <c r="O16">
-        <v>4.993919695874431</v>
+        <v>4.95324181155131</v>
       </c>
       <c r="P16">
-        <v>29.21100972792304</v>
+        <v>28.97307196619739</v>
       </c>
       <c r="Q16">
-        <v>62.81100972792304</v>
+        <v>62.57307196619739</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09188776209852897</v>
+        <v>0.09236047071959226</v>
       </c>
       <c r="T16">
-        <v>1.064382496501824</v>
+        <v>1.075299554724994</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.69166370848577</v>
+        <v>12.40884116282584</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08514198011165343</v>
+        <v>0.08506727681857192</v>
       </c>
       <c r="C17">
-        <v>329.096630241823</v>
+        <v>325.908716173639</v>
       </c>
       <c r="D17">
-        <v>336.0037001694542</v>
+        <v>336.6429240964457</v>
       </c>
       <c r="E17">
-        <v>22.99327041008943</v>
+        <v>26.82040840526486</v>
       </c>
       <c r="F17">
-        <v>57.40706992763128</v>
+        <v>61.2342079228067</v>
       </c>
       <c r="G17">
         <v>50.5</v>
@@ -2663,28 +2663,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M17">
-        <v>2.9736862222513</v>
+        <v>3.171931970401387</v>
       </c>
       <c r="N17">
-        <v>33.9263137777487</v>
+        <v>33.72806802959862</v>
       </c>
       <c r="O17">
-        <v>4.95324181155131</v>
+        <v>4.924297932321398</v>
       </c>
       <c r="P17">
-        <v>28.97307196619739</v>
+        <v>28.80377009727722</v>
       </c>
       <c r="Q17">
-        <v>62.57307196619739</v>
+        <v>62.40377009727722</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09236047071959226</v>
+        <v>0.09284443430782371</v>
       </c>
       <c r="T17">
-        <v>1.075299554724994</v>
+        <v>1.086476542905859</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.40884116282584</v>
+        <v>11.63328859014922</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08506727681857192</v>
+        <v>0.0849925735254904</v>
       </c>
       <c r="C18">
-        <v>325.908716173639</v>
+        <v>322.7232389003919</v>
       </c>
       <c r="D18">
-        <v>336.6429240964457</v>
+        <v>337.284584818374</v>
       </c>
       <c r="E18">
-        <v>26.82040840526486</v>
+        <v>30.64754640044028</v>
       </c>
       <c r="F18">
-        <v>61.2342079228067</v>
+        <v>65.06134591798212</v>
       </c>
       <c r="G18">
         <v>50.5</v>
@@ -2745,28 +2745,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M18">
-        <v>3.171931970401387</v>
+        <v>3.370177718551474</v>
       </c>
       <c r="N18">
-        <v>33.72806802959862</v>
+        <v>33.52982228144853</v>
       </c>
       <c r="O18">
-        <v>4.924297932321398</v>
+        <v>4.895354053091485</v>
       </c>
       <c r="P18">
-        <v>28.80377009727722</v>
+        <v>28.63446822835705</v>
       </c>
       <c r="Q18">
-        <v>62.40377009727722</v>
+        <v>62.23446822835704</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09284443430782371</v>
+        <v>0.09334005966926556</v>
       </c>
       <c r="T18">
-        <v>1.086476542905859</v>
+        <v>1.097922856103131</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.63328859014922</v>
+        <v>10.94897749661103</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0849925735254904</v>
+        <v>0.0849178702324089</v>
       </c>
       <c r="C19">
-        <v>322.7232389003919</v>
+        <v>319.5402123827039</v>
       </c>
       <c r="D19">
-        <v>337.284584818374</v>
+        <v>337.9286962958615</v>
       </c>
       <c r="E19">
-        <v>30.64754640044028</v>
+        <v>34.4746843956157</v>
       </c>
       <c r="F19">
-        <v>65.06134591798212</v>
+        <v>68.88848391315754</v>
       </c>
       <c r="G19">
         <v>50.5</v>
@@ -2827,28 +2827,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M19">
-        <v>3.370177718551474</v>
+        <v>3.568423466701561</v>
       </c>
       <c r="N19">
-        <v>33.52982228144853</v>
+        <v>33.33157653329845</v>
       </c>
       <c r="O19">
-        <v>4.895354053091485</v>
+        <v>4.866410173861572</v>
       </c>
       <c r="P19">
-        <v>28.63446822835705</v>
+        <v>28.46516635943687</v>
       </c>
       <c r="Q19">
-        <v>62.23446822835704</v>
+        <v>62.06516635943687</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09334005966926556</v>
+        <v>0.09384777345415721</v>
       </c>
       <c r="T19">
-        <v>1.097922856103131</v>
+        <v>1.109648347671067</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.94897749661103</v>
+        <v>10.34070096902153</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08491787023240892</v>
+        <v>0.08511900893932743</v>
       </c>
       <c r="C20">
-        <v>319.5402123827038</v>
+        <v>313.9843802307532</v>
       </c>
       <c r="D20">
-        <v>337.9286962958614</v>
+        <v>336.2000021390862</v>
       </c>
       <c r="E20">
-        <v>34.47468439561568</v>
+        <v>38.30182239079112</v>
       </c>
       <c r="F20">
-        <v>68.88848391315753</v>
+        <v>72.71562190833296</v>
       </c>
       <c r="G20">
         <v>50.5</v>
@@ -2909,45 +2909,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M20">
-        <v>3.56842346670156</v>
+        <v>3.890285772095813</v>
       </c>
       <c r="N20">
-        <v>33.33157653329845</v>
+        <v>33.00971422790419</v>
       </c>
       <c r="O20">
-        <v>4.866410173861572</v>
+        <v>4.819418277274012</v>
       </c>
       <c r="P20">
-        <v>28.46516635943687</v>
+        <v>28.19029595063018</v>
       </c>
       <c r="Q20">
-        <v>62.06516635943687</v>
+        <v>61.79029595063017</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09384777345415721</v>
+        <v>0.09436802338188571</v>
       </c>
       <c r="T20">
-        <v>1.109648347671067</v>
+        <v>1.121663357549323</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.34070096902154</v>
+        <v>9.485164371387778</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08511900893932743</v>
+        <v>0.08505882364624594</v>
       </c>
       <c r="C21">
-        <v>313.9843802307532</v>
+        <v>310.6726498250936</v>
       </c>
       <c r="D21">
-        <v>336.2000021390862</v>
+        <v>336.715409728602</v>
       </c>
       <c r="E21">
-        <v>38.30182239079112</v>
+        <v>42.12896038596654</v>
       </c>
       <c r="F21">
-        <v>72.71562190833296</v>
+        <v>76.54275990350838</v>
       </c>
       <c r="G21">
         <v>50.5</v>
@@ -2991,28 +2991,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M21">
-        <v>3.890285772095813</v>
+        <v>4.095037654837698</v>
       </c>
       <c r="N21">
-        <v>33.00971422790419</v>
+        <v>32.80496234516231</v>
       </c>
       <c r="O21">
-        <v>4.819418277274012</v>
+        <v>4.789524502393697</v>
       </c>
       <c r="P21">
-        <v>28.19029595063018</v>
+        <v>28.01543784276861</v>
       </c>
       <c r="Q21">
-        <v>61.79029595063017</v>
+        <v>61.61543784276861</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09436802338188571</v>
+        <v>0.09490127955780742</v>
       </c>
       <c r="T21">
-        <v>1.121663357549323</v>
+        <v>1.133978742674536</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.485164371387778</v>
+        <v>9.010906152818391</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08505882364624594</v>
+        <v>0.08499863835316443</v>
       </c>
       <c r="C22">
-        <v>310.6726498250936</v>
+        <v>307.3625021252695</v>
       </c>
       <c r="D22">
-        <v>336.715409728602</v>
+        <v>337.2324000239533</v>
       </c>
       <c r="E22">
-        <v>42.12896038596654</v>
+        <v>45.95609838114196</v>
       </c>
       <c r="F22">
-        <v>76.54275990350838</v>
+        <v>80.3698978986838</v>
       </c>
       <c r="G22">
         <v>50.5</v>
@@ -3073,28 +3073,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M22">
-        <v>4.095037654837698</v>
+        <v>4.299789537579583</v>
       </c>
       <c r="N22">
-        <v>32.80496234516231</v>
+        <v>32.60021046242042</v>
       </c>
       <c r="O22">
-        <v>4.789524502393697</v>
+        <v>4.759630727513382</v>
       </c>
       <c r="P22">
-        <v>28.01543784276861</v>
+        <v>27.84057973490704</v>
       </c>
       <c r="Q22">
-        <v>61.61543784276861</v>
+        <v>61.44057973490703</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09490127955780742</v>
+        <v>0.09544803589008155</v>
       </c>
       <c r="T22">
-        <v>1.133978742674536</v>
+        <v>1.146605909701652</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.010906152818391</v>
+        <v>8.581815383636561</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08499863835316443</v>
+        <v>0.08493845306008294</v>
       </c>
       <c r="C23">
-        <v>307.3625021252695</v>
+        <v>304.0539444327152</v>
       </c>
       <c r="D23">
-        <v>337.2324000239533</v>
+        <v>337.7509803265744</v>
       </c>
       <c r="E23">
-        <v>45.95609838114194</v>
+        <v>49.78323637631736</v>
       </c>
       <c r="F23">
-        <v>80.36989789868379</v>
+        <v>84.19703589385921</v>
       </c>
       <c r="G23">
         <v>50.5</v>
@@ -3155,28 +3155,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M23">
-        <v>4.299789537579582</v>
+        <v>4.504541420321468</v>
       </c>
       <c r="N23">
-        <v>32.60021046242042</v>
+        <v>32.39545857967854</v>
       </c>
       <c r="O23">
-        <v>4.759630727513382</v>
+        <v>4.729736952633067</v>
       </c>
       <c r="P23">
-        <v>27.84057973490704</v>
+        <v>27.66572162704547</v>
       </c>
       <c r="Q23">
-        <v>61.44057973490703</v>
+        <v>61.26572162704547</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09544803589008155</v>
+        <v>0.09600881161549094</v>
       </c>
       <c r="T23">
-        <v>1.146605909701652</v>
+        <v>1.159556850242285</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.581815383636563</v>
+        <v>8.191732866198537</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08493845306008294</v>
+        <v>0.08487826776700144</v>
       </c>
       <c r="C24">
-        <v>304.0539444327152</v>
+        <v>300.7469840938453</v>
       </c>
       <c r="D24">
-        <v>337.7509803265744</v>
+        <v>338.2711579828799</v>
       </c>
       <c r="E24">
-        <v>49.78323637631736</v>
+        <v>53.61037437149278</v>
       </c>
       <c r="F24">
-        <v>84.19703589385921</v>
+        <v>88.02417388903463</v>
       </c>
       <c r="G24">
         <v>50.5</v>
@@ -3237,28 +3237,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M24">
-        <v>4.504541420321468</v>
+        <v>4.709293303063353</v>
       </c>
       <c r="N24">
-        <v>32.39545857967854</v>
+        <v>32.19070669693665</v>
       </c>
       <c r="O24">
-        <v>4.729736952633067</v>
+        <v>4.699843177752751</v>
       </c>
       <c r="P24">
-        <v>27.66572162704547</v>
+        <v>27.4908635191839</v>
       </c>
       <c r="Q24">
-        <v>61.26572162704547</v>
+        <v>61.0908635191839</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09600881161549094</v>
+        <v>0.0965841529441577</v>
       </c>
       <c r="T24">
-        <v>1.159556850242285</v>
+        <v>1.172844178848907</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.191732866198537</v>
+        <v>7.835570567668166</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08487826776700144</v>
+        <v>0.08498205047391993</v>
       </c>
       <c r="C25">
-        <v>300.7469840938453</v>
+        <v>296.0238568376871</v>
       </c>
       <c r="D25">
-        <v>338.2711579828799</v>
+        <v>337.3751687218972</v>
       </c>
       <c r="E25">
-        <v>53.61037437149278</v>
+        <v>57.43751236666822</v>
       </c>
       <c r="F25">
-        <v>88.02417388903463</v>
+        <v>91.85131188421006</v>
       </c>
       <c r="G25">
         <v>50.5</v>
@@ -3319,45 +3319,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M25">
-        <v>4.709293303063353</v>
+        <v>4.987526235312607</v>
       </c>
       <c r="N25">
-        <v>32.19070669693665</v>
+        <v>31.9124737646874</v>
       </c>
       <c r="O25">
-        <v>4.699843177752751</v>
+        <v>4.65922116964436</v>
       </c>
       <c r="P25">
-        <v>27.4908635191839</v>
+        <v>27.25325259504304</v>
       </c>
       <c r="Q25">
-        <v>61.0908635191839</v>
+        <v>60.85325259504303</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0965841529441577</v>
+        <v>0.09717463483410517</v>
       </c>
       <c r="T25">
-        <v>1.172844178848907</v>
+        <v>1.18648117399781</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.835570567668166</v>
+        <v>7.398457323139715</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08498205047391993</v>
+        <v>0.08492869718083843</v>
       </c>
       <c r="C26">
-        <v>296.0238568376872</v>
+        <v>292.6567412187246</v>
       </c>
       <c r="D26">
-        <v>337.3751687218972</v>
+        <v>337.83519109811</v>
       </c>
       <c r="E26">
-        <v>57.4375123666682</v>
+        <v>61.26465036184362</v>
       </c>
       <c r="F26">
-        <v>91.85131188421005</v>
+        <v>95.67844987938547</v>
       </c>
       <c r="G26">
         <v>50.5</v>
@@ -3401,28 +3401,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M26">
-        <v>4.987526235312606</v>
+        <v>5.195339828450631</v>
       </c>
       <c r="N26">
-        <v>31.9124737646874</v>
+        <v>31.70466017154937</v>
       </c>
       <c r="O26">
-        <v>4.65922116964436</v>
+        <v>4.628880385046209</v>
       </c>
       <c r="P26">
-        <v>27.25325259504304</v>
+        <v>27.07577978650317</v>
       </c>
       <c r="Q26">
-        <v>60.85325259504303</v>
+        <v>60.67577978650316</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09717463483410517</v>
+        <v>0.09778086290778457</v>
       </c>
       <c r="T26">
-        <v>1.18648117399781</v>
+        <v>1.200481822350683</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.398457323139715</v>
+        <v>7.102519030214126</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08492869718083843</v>
+        <v>0.08487534388775694</v>
       </c>
       <c r="C27">
-        <v>292.6567412187246</v>
+        <v>289.2908818245941</v>
       </c>
       <c r="D27">
-        <v>337.83519109811</v>
+        <v>338.296469699155</v>
       </c>
       <c r="E27">
-        <v>61.26465036184362</v>
+        <v>65.09178835701904</v>
       </c>
       <c r="F27">
-        <v>95.67844987938547</v>
+        <v>99.50558787456089</v>
       </c>
       <c r="G27">
         <v>50.5</v>
@@ -3483,28 +3483,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M27">
-        <v>5.195339828450631</v>
+        <v>5.403153421588656</v>
       </c>
       <c r="N27">
-        <v>31.70466017154937</v>
+        <v>31.49684657841135</v>
       </c>
       <c r="O27">
-        <v>4.628880385046209</v>
+        <v>4.598539600448057</v>
       </c>
       <c r="P27">
-        <v>27.07577978650317</v>
+        <v>26.89830697796329</v>
       </c>
       <c r="Q27">
-        <v>60.67577978650316</v>
+        <v>60.49830697796329</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09778086290778457</v>
+        <v>0.09840347552399586</v>
       </c>
       <c r="T27">
-        <v>1.200481822350683</v>
+        <v>1.214860866604985</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.102519030214126</v>
+        <v>6.829345221359738</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08487534388775694</v>
+        <v>0.08482199059467543</v>
       </c>
       <c r="C28">
-        <v>289.2908818245941</v>
+        <v>285.9262838080625</v>
       </c>
       <c r="D28">
-        <v>338.296469699155</v>
+        <v>338.7590096777988</v>
       </c>
       <c r="E28">
-        <v>65.09178835701904</v>
+        <v>68.91892635219446</v>
       </c>
       <c r="F28">
-        <v>99.50558787456089</v>
+        <v>103.3327258697363</v>
       </c>
       <c r="G28">
         <v>50.5</v>
@@ -3565,28 +3565,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M28">
-        <v>5.403153421588656</v>
+        <v>5.610967014726682</v>
       </c>
       <c r="N28">
-        <v>31.49684657841135</v>
+        <v>31.28903298527332</v>
       </c>
       <c r="O28">
-        <v>4.598539600448057</v>
+        <v>4.568198815849905</v>
       </c>
       <c r="P28">
-        <v>26.89830697796329</v>
+        <v>26.72083416942342</v>
       </c>
       <c r="Q28">
-        <v>60.49830697796329</v>
+        <v>60.32083416942341</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09840347552399586</v>
+        <v>0.09904314602010333</v>
       </c>
       <c r="T28">
-        <v>1.214860866604985</v>
+        <v>1.229633857277213</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.829345221359738</v>
+        <v>6.576406509457525</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08482199059467543</v>
+        <v>0.08476863730159394</v>
       </c>
       <c r="C29">
-        <v>285.9262838080625</v>
+        <v>282.5629523501148</v>
       </c>
       <c r="D29">
-        <v>338.7590096777988</v>
+        <v>339.2228162150265</v>
       </c>
       <c r="E29">
-        <v>68.91892635219446</v>
+        <v>72.74606434736988</v>
       </c>
       <c r="F29">
-        <v>103.3327258697363</v>
+        <v>107.1598638649117</v>
       </c>
       <c r="G29">
         <v>50.5</v>
@@ -3647,28 +3647,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M29">
-        <v>5.610967014726682</v>
+        <v>5.818780607864707</v>
       </c>
       <c r="N29">
-        <v>31.28903298527332</v>
+        <v>31.0812193921353</v>
       </c>
       <c r="O29">
-        <v>4.568198815849905</v>
+        <v>4.537858031251753</v>
       </c>
       <c r="P29">
-        <v>26.72083416942342</v>
+        <v>26.54336136088354</v>
       </c>
       <c r="Q29">
-        <v>60.32083416942341</v>
+        <v>60.14336136088354</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09904314602010333</v>
+        <v>0.09970058514110269</v>
       </c>
       <c r="T29">
-        <v>1.229633857277213</v>
+        <v>1.244817208801448</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.576406509457525</v>
+        <v>6.341534848405471</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08476863730159394</v>
+        <v>0.08471528400851244</v>
       </c>
       <c r="C30">
-        <v>282.5629523501148</v>
+        <v>279.2008926601496</v>
       </c>
       <c r="D30">
-        <v>339.2228162150265</v>
+        <v>339.6878945202367</v>
       </c>
       <c r="E30">
-        <v>72.74606434736988</v>
+        <v>76.57320234254531</v>
       </c>
       <c r="F30">
-        <v>107.1598638649117</v>
+        <v>110.9870018600872</v>
       </c>
       <c r="G30">
         <v>50.5</v>
@@ -3729,28 +3729,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M30">
-        <v>5.818780607864707</v>
+        <v>6.026594201002733</v>
       </c>
       <c r="N30">
-        <v>31.0812193921353</v>
+        <v>30.87340579899727</v>
       </c>
       <c r="O30">
-        <v>4.537858031251753</v>
+        <v>4.507517246653602</v>
       </c>
       <c r="P30">
-        <v>26.54336136088354</v>
+        <v>26.36588855234367</v>
       </c>
       <c r="Q30">
-        <v>60.14336136088354</v>
+        <v>59.96588855234366</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09970058514110269</v>
+        <v>0.1003765436739612</v>
       </c>
       <c r="T30">
-        <v>1.244817208801448</v>
+        <v>1.260428260368618</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.341534848405471</v>
+        <v>6.122861232943212</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08471528400851244</v>
+        <v>0.08491813071543093</v>
       </c>
       <c r="C31">
-        <v>279.2008926601496</v>
+        <v>273.6123062132381</v>
       </c>
       <c r="D31">
-        <v>339.6878945202367</v>
+        <v>337.9264460685006</v>
       </c>
       <c r="E31">
-        <v>76.57320234254529</v>
+        <v>80.40034033772071</v>
       </c>
       <c r="F31">
-        <v>110.9870018600871</v>
+        <v>114.8141398552626</v>
       </c>
       <c r="G31">
         <v>50.5</v>
@@ -3811,45 +3811,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M31">
-        <v>6.026594201002731</v>
+        <v>6.349221933996019</v>
       </c>
       <c r="N31">
-        <v>30.87340579899728</v>
+        <v>30.55077806600399</v>
       </c>
       <c r="O31">
-        <v>4.507517246653602</v>
+        <v>4.460413597636582</v>
       </c>
       <c r="P31">
-        <v>26.36588855234367</v>
+        <v>26.0903644683674</v>
       </c>
       <c r="Q31">
-        <v>59.96588855234367</v>
+        <v>59.6903644683674</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1003765436739612</v>
+        <v>0.1010718153077585</v>
       </c>
       <c r="T31">
-        <v>1.260428260368618</v>
+        <v>1.276485341980565</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.122861232943214</v>
+        <v>5.811735734488052</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08491813071543093</v>
+        <v>0.08487331742234944</v>
       </c>
       <c r="C32">
-        <v>273.6123062132381</v>
+        <v>270.1727369700058</v>
       </c>
       <c r="D32">
-        <v>337.9264460685006</v>
+        <v>338.3140148204437</v>
       </c>
       <c r="E32">
-        <v>80.40034033772071</v>
+        <v>84.22747833289613</v>
       </c>
       <c r="F32">
-        <v>114.8141398552626</v>
+        <v>118.641277850438</v>
       </c>
       <c r="G32">
         <v>50.5</v>
@@ -3893,28 +3893,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M32">
-        <v>6.349221933996019</v>
+        <v>6.56086266512922</v>
       </c>
       <c r="N32">
-        <v>30.55077806600399</v>
+        <v>30.33913733487078</v>
       </c>
       <c r="O32">
-        <v>4.460413597636582</v>
+        <v>4.429514050891134</v>
       </c>
       <c r="P32">
-        <v>26.0903644683674</v>
+        <v>25.90962328397965</v>
       </c>
       <c r="Q32">
-        <v>59.6903644683674</v>
+        <v>59.50962328397964</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1010718153077585</v>
+        <v>0.1017872397425354</v>
       </c>
       <c r="T32">
-        <v>1.276485341980565</v>
+        <v>1.293007846247931</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.811735734488052</v>
+        <v>5.624260388214243</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08487331742234944</v>
+        <v>0.08482850412926794</v>
       </c>
       <c r="C33">
-        <v>270.1727369700058</v>
+        <v>266.7340577548417</v>
       </c>
       <c r="D33">
-        <v>338.3140148204437</v>
+        <v>338.7024736004551</v>
       </c>
       <c r="E33">
-        <v>84.22747833289613</v>
+        <v>88.05461632807156</v>
       </c>
       <c r="F33">
-        <v>118.641277850438</v>
+        <v>122.4684158456134</v>
       </c>
       <c r="G33">
         <v>50.5</v>
@@ -3975,28 +3975,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M33">
-        <v>6.56086266512922</v>
+        <v>6.772503396262421</v>
       </c>
       <c r="N33">
-        <v>30.33913733487078</v>
+        <v>30.12749660373758</v>
       </c>
       <c r="O33">
-        <v>4.429514050891134</v>
+        <v>4.398614504145687</v>
       </c>
       <c r="P33">
-        <v>25.90962328397965</v>
+        <v>25.7288820995919</v>
       </c>
       <c r="Q33">
-        <v>59.50962328397964</v>
+        <v>59.32888209959189</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1017872397425354</v>
+        <v>0.1025237060724529</v>
       </c>
       <c r="T33">
-        <v>1.293007846247931</v>
+        <v>1.31001630652316</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.624260388214243</v>
+        <v>5.448502251082548</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08482850412926794</v>
+        <v>0.08478369083618645</v>
       </c>
       <c r="C34">
-        <v>266.7340577548417</v>
+        <v>263.2962716371133</v>
       </c>
       <c r="D34">
-        <v>338.7024736004551</v>
+        <v>339.0918254779021</v>
       </c>
       <c r="E34">
-        <v>88.05461632807156</v>
+        <v>91.88175432324698</v>
       </c>
       <c r="F34">
-        <v>122.4684158456134</v>
+        <v>126.2955538407888</v>
       </c>
       <c r="G34">
         <v>50.5</v>
@@ -4057,28 +4057,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M34">
-        <v>6.772503396262421</v>
+        <v>6.984144127395623</v>
       </c>
       <c r="N34">
-        <v>30.12749660373758</v>
+        <v>29.91585587260438</v>
       </c>
       <c r="O34">
-        <v>4.398614504145687</v>
+        <v>4.367714957400239</v>
       </c>
       <c r="P34">
-        <v>25.7288820995919</v>
+        <v>25.54814091520414</v>
       </c>
       <c r="Q34">
-        <v>59.32888209959189</v>
+        <v>59.14814091520414</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1025237060724529</v>
+        <v>0.1032821564719201</v>
       </c>
       <c r="T34">
-        <v>1.31001630652316</v>
+        <v>1.327532482030486</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.448502251082548</v>
+        <v>5.283396122261864</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08478369083618645</v>
+        <v>0.08473887754310494</v>
       </c>
       <c r="C35">
-        <v>263.2962716371133</v>
+        <v>259.8593817003177</v>
       </c>
       <c r="D35">
-        <v>339.0918254779021</v>
+        <v>339.4820735362819</v>
       </c>
       <c r="E35">
-        <v>91.88175432324698</v>
+        <v>95.7088923184224</v>
       </c>
       <c r="F35">
-        <v>126.2955538407888</v>
+        <v>130.1226918359642</v>
       </c>
       <c r="G35">
         <v>50.5</v>
@@ -4139,28 +4139,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M35">
-        <v>6.984144127395623</v>
+        <v>7.195784858528823</v>
       </c>
       <c r="N35">
-        <v>29.91585587260438</v>
+        <v>29.70421514147118</v>
       </c>
       <c r="O35">
-        <v>4.367714957400239</v>
+        <v>4.336815410654792</v>
       </c>
       <c r="P35">
-        <v>25.54814091520414</v>
+        <v>25.36739973081639</v>
       </c>
       <c r="Q35">
-        <v>59.14814091520414</v>
+        <v>58.96739973081638</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1032821564719201</v>
+        <v>0.1040635902168257</v>
       </c>
       <c r="T35">
-        <v>1.327532482030486</v>
+        <v>1.345579450735004</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.283396122261864</v>
+        <v>5.128002118665927</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08473887754310494</v>
+        <v>0.08469406425002343</v>
       </c>
       <c r="C36">
-        <v>259.8593817003177</v>
+        <v>256.4233910421627</v>
       </c>
       <c r="D36">
-        <v>339.4820735362819</v>
+        <v>339.8732208733024</v>
       </c>
       <c r="E36">
-        <v>95.7088923184224</v>
+        <v>99.53603031359783</v>
       </c>
       <c r="F36">
-        <v>130.1226918359642</v>
+        <v>133.9498298311397</v>
       </c>
       <c r="G36">
         <v>50.5</v>
@@ -4221,28 +4221,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M36">
-        <v>7.195784858528823</v>
+        <v>7.407425589662025</v>
       </c>
       <c r="N36">
-        <v>29.70421514147118</v>
+        <v>29.49257441033798</v>
       </c>
       <c r="O36">
-        <v>4.336815410654792</v>
+        <v>4.305915863909345</v>
       </c>
       <c r="P36">
-        <v>25.36739973081639</v>
+        <v>25.18665854642864</v>
       </c>
       <c r="Q36">
-        <v>58.96739973081638</v>
+        <v>58.78665854642863</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1040635902168257</v>
+        <v>0.1048690680769591</v>
       </c>
       <c r="T36">
-        <v>1.345579450735004</v>
+        <v>1.364181710784276</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.128002118665927</v>
+        <v>4.981487772418328</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08469406425002343</v>
+        <v>0.08464925095694195</v>
       </c>
       <c r="C37">
-        <v>256.4233910421627</v>
+        <v>252.9883027746493</v>
       </c>
       <c r="D37">
-        <v>339.8732208733024</v>
+        <v>340.2652706009644</v>
       </c>
       <c r="E37">
-        <v>99.53603031359783</v>
+        <v>103.3631683087732</v>
       </c>
       <c r="F37">
-        <v>133.9498298311397</v>
+        <v>137.7769678263151</v>
       </c>
       <c r="G37">
         <v>50.5</v>
@@ -4303,28 +4303,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M37">
-        <v>7.407425589662025</v>
+        <v>7.619066320795224</v>
       </c>
       <c r="N37">
-        <v>29.49257441033798</v>
+        <v>29.28093367920478</v>
       </c>
       <c r="O37">
-        <v>4.305915863909345</v>
+        <v>4.275016317163898</v>
       </c>
       <c r="P37">
-        <v>25.18665854642864</v>
+        <v>25.00591736204088</v>
       </c>
       <c r="Q37">
-        <v>58.78665854642863</v>
+        <v>58.60591736204088</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1048690680769591</v>
+        <v>0.1056997171202218</v>
       </c>
       <c r="T37">
-        <v>1.364181710784276</v>
+        <v>1.383365291460087</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.981487772418328</v>
+        <v>4.843113112073376</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08464925095694194</v>
+        <v>0.08460443766386046</v>
       </c>
       <c r="C38">
-        <v>252.9883027746495</v>
+        <v>249.5541200241545</v>
       </c>
       <c r="D38">
-        <v>340.2652706009645</v>
+        <v>340.6582258456449</v>
       </c>
       <c r="E38">
-        <v>103.3631683087732</v>
+        <v>107.1903063039486</v>
       </c>
       <c r="F38">
-        <v>137.7769678263151</v>
+        <v>141.6041058214905</v>
       </c>
       <c r="G38">
         <v>50.5</v>
@@ -4385,28 +4385,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M38">
-        <v>7.619066320795223</v>
+        <v>7.830707051928425</v>
       </c>
       <c r="N38">
-        <v>29.28093367920478</v>
+        <v>29.06929294807158</v>
       </c>
       <c r="O38">
-        <v>4.275016317163898</v>
+        <v>4.244116770418451</v>
       </c>
       <c r="P38">
-        <v>25.00591736204088</v>
+        <v>24.82517617765313</v>
       </c>
       <c r="Q38">
-        <v>58.60591736204088</v>
+        <v>58.42517617765313</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1056997171202218</v>
+        <v>0.1065567359743817</v>
       </c>
       <c r="T38">
-        <v>1.383365291460087</v>
+        <v>1.403157874697036</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.843113112073377</v>
+        <v>4.71221816309842</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08460443766386046</v>
+        <v>0.08455962437077895</v>
       </c>
       <c r="C39">
-        <v>249.5541200241545</v>
+        <v>246.1208459315137</v>
       </c>
       <c r="D39">
-        <v>340.6582258456449</v>
+        <v>341.0520897481796</v>
       </c>
       <c r="E39">
-        <v>107.1903063039486</v>
+        <v>111.0174442991241</v>
       </c>
       <c r="F39">
-        <v>141.6041058214905</v>
+        <v>145.4312438166659</v>
       </c>
       <c r="G39">
         <v>50.5</v>
@@ -4467,28 +4467,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M39">
-        <v>7.830707051928425</v>
+        <v>8.042347783061626</v>
       </c>
       <c r="N39">
-        <v>29.06929294807158</v>
+        <v>28.85765221693838</v>
       </c>
       <c r="O39">
-        <v>4.244116770418451</v>
+        <v>4.213217223673003</v>
       </c>
       <c r="P39">
-        <v>24.82517617765313</v>
+        <v>24.64443499326538</v>
       </c>
       <c r="Q39">
-        <v>58.42517617765313</v>
+        <v>58.24443499326537</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1065567359743817</v>
+        <v>0.1074414005980306</v>
       </c>
       <c r="T39">
-        <v>1.403157874697036</v>
+        <v>1.423588928360983</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.71221816309842</v>
+        <v>4.588212421964251</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08455962437077895</v>
+        <v>0.08534746107769746</v>
       </c>
       <c r="C40">
-        <v>246.1208459315137</v>
+        <v>235.4995080571857</v>
       </c>
       <c r="D40">
-        <v>341.0520897481796</v>
+        <v>334.257889869027</v>
       </c>
       <c r="E40">
-        <v>111.0174442991241</v>
+        <v>114.8445822942995</v>
       </c>
       <c r="F40">
-        <v>145.4312438166659</v>
+        <v>149.2583818118413</v>
       </c>
       <c r="G40">
         <v>50.5</v>
@@ -4549,45 +4549,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M40">
-        <v>8.042347783061626</v>
+        <v>8.62713446872443</v>
       </c>
       <c r="N40">
-        <v>28.85765221693838</v>
+        <v>28.27286553127558</v>
       </c>
       <c r="O40">
-        <v>4.213217223673003</v>
+        <v>4.127838367566234</v>
       </c>
       <c r="P40">
-        <v>24.64443499326538</v>
+        <v>24.14502716370934</v>
       </c>
       <c r="Q40">
-        <v>58.24443499326537</v>
+        <v>57.74502716370934</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1074414005980306</v>
+        <v>0.1083550706191762</v>
       </c>
       <c r="T40">
-        <v>1.423588928360983</v>
+        <v>1.444689852636862</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.588212421964251</v>
+        <v>4.277202370470977</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08534746107769746</v>
+        <v>0.08532399778461594</v>
       </c>
       <c r="C41">
-        <v>235.4995080571857</v>
+        <v>231.8708011741043</v>
       </c>
       <c r="D41">
-        <v>334.257889869027</v>
+        <v>334.4563209811211</v>
       </c>
       <c r="E41">
-        <v>114.8445822942995</v>
+        <v>118.6717202894749</v>
       </c>
       <c r="F41">
-        <v>149.2583818118413</v>
+        <v>153.0855198070168</v>
       </c>
       <c r="G41">
         <v>50.5</v>
@@ -4631,28 +4631,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M41">
-        <v>8.62713446872443</v>
+        <v>8.848343044845569</v>
       </c>
       <c r="N41">
-        <v>28.27286553127558</v>
+        <v>28.05165695515444</v>
       </c>
       <c r="O41">
-        <v>4.127838367566234</v>
+        <v>4.095541915452547</v>
       </c>
       <c r="P41">
-        <v>24.14502716370934</v>
+        <v>23.95611503970189</v>
       </c>
       <c r="Q41">
-        <v>57.74502716370934</v>
+        <v>57.55611503970188</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1083550706191762</v>
+        <v>0.1092991963076932</v>
       </c>
       <c r="T41">
-        <v>1.444689852636862</v>
+        <v>1.466494141055271</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.277202370470977</v>
+        <v>4.170272311209203</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08532399778461594</v>
+        <v>0.08530053449153445</v>
       </c>
       <c r="C42">
-        <v>231.8708011741043</v>
+        <v>228.2423300269388</v>
       </c>
       <c r="D42">
-        <v>334.4563209811211</v>
+        <v>334.654987829131</v>
       </c>
       <c r="E42">
-        <v>118.6717202894749</v>
+        <v>122.4988582846503</v>
       </c>
       <c r="F42">
-        <v>153.0855198070168</v>
+        <v>156.9126578021922</v>
       </c>
       <c r="G42">
         <v>50.5</v>
@@ -4713,28 +4713,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M42">
-        <v>8.848343044845569</v>
+        <v>9.069551620966708</v>
       </c>
       <c r="N42">
-        <v>28.05165695515444</v>
+        <v>27.8304483790333</v>
       </c>
       <c r="O42">
-        <v>4.095541915452547</v>
+        <v>4.063245463338862</v>
       </c>
       <c r="P42">
-        <v>23.95611503970189</v>
+        <v>23.76720291569444</v>
       </c>
       <c r="Q42">
-        <v>57.55611503970188</v>
+        <v>57.36720291569443</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1092991963076932</v>
+        <v>0.1102753262568381</v>
       </c>
       <c r="T42">
-        <v>1.466494141055271</v>
+        <v>1.489037557894643</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.170272311209203</v>
+        <v>4.068558352399222</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08530053449153445</v>
+        <v>0.08653245119845296</v>
       </c>
       <c r="C43">
-        <v>228.2423300269388</v>
+        <v>214.2938499953682</v>
       </c>
       <c r="D43">
-        <v>334.654987829131</v>
+        <v>324.5336457927358</v>
       </c>
       <c r="E43">
-        <v>122.4988582846503</v>
+        <v>126.3259962798258</v>
       </c>
       <c r="F43">
-        <v>156.9126578021922</v>
+        <v>160.7397957973676</v>
       </c>
       <c r="G43">
         <v>50.5</v>
@@ -4795,45 +4795,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M43">
-        <v>9.069551620966708</v>
+        <v>9.853349482378635</v>
       </c>
       <c r="N43">
-        <v>27.8304483790333</v>
+        <v>27.04665051762137</v>
       </c>
       <c r="O43">
-        <v>4.063245463338862</v>
+        <v>3.94881097557272</v>
       </c>
       <c r="P43">
-        <v>23.76720291569444</v>
+        <v>23.09783954204865</v>
       </c>
       <c r="Q43">
-        <v>57.36720291569443</v>
+        <v>56.69783954204865</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1102753262568381</v>
+        <v>0.1112851158594017</v>
       </c>
       <c r="T43">
-        <v>1.489037557894643</v>
+        <v>1.512358333935373</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.068558352399222</v>
+        <v>3.744919437394421</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08653245119845296</v>
+        <v>0.08653887790537146</v>
       </c>
       <c r="C44">
-        <v>214.2938499953682</v>
+        <v>210.4155156311728</v>
       </c>
       <c r="D44">
-        <v>324.5336457927358</v>
+        <v>324.4824494237158</v>
       </c>
       <c r="E44">
-        <v>126.3259962798257</v>
+        <v>130.1531342750012</v>
       </c>
       <c r="F44">
-        <v>160.7397957973676</v>
+        <v>164.566933792543</v>
       </c>
       <c r="G44">
         <v>50.5</v>
@@ -4877,28 +4877,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M44">
-        <v>9.853349482378633</v>
+        <v>10.08795304148289</v>
       </c>
       <c r="N44">
-        <v>27.04665051762137</v>
+        <v>26.81204695851712</v>
       </c>
       <c r="O44">
-        <v>3.94881097557272</v>
+        <v>3.914558855943499</v>
       </c>
       <c r="P44">
-        <v>23.09783954204865</v>
+        <v>22.89748810257362</v>
       </c>
       <c r="Q44">
-        <v>56.69783954204865</v>
+        <v>56.49748810257361</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1112851158594016</v>
+        <v>0.1123303366760903</v>
       </c>
       <c r="T44">
-        <v>1.512358333935372</v>
+        <v>1.536497382819636</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.744919437394422</v>
+        <v>3.657828287687574</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08653887790537146</v>
+        <v>0.08654530461228996</v>
       </c>
       <c r="C45">
-        <v>210.4155156311728</v>
+        <v>206.5371974172584</v>
       </c>
       <c r="D45">
-        <v>324.4824494237158</v>
+        <v>324.4312692049768</v>
       </c>
       <c r="E45">
-        <v>130.1531342750012</v>
+        <v>133.9802722701766</v>
       </c>
       <c r="F45">
-        <v>164.566933792543</v>
+        <v>168.3940717877184</v>
       </c>
       <c r="G45">
         <v>50.5</v>
@@ -4959,28 +4959,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M45">
-        <v>10.08795304148289</v>
+        <v>10.32255660058714</v>
       </c>
       <c r="N45">
-        <v>26.81204695851712</v>
+        <v>26.57744339941286</v>
       </c>
       <c r="O45">
-        <v>3.914558855943499</v>
+        <v>3.880306736314278</v>
       </c>
       <c r="P45">
-        <v>22.89748810257362</v>
+        <v>22.69713666309859</v>
       </c>
       <c r="Q45">
-        <v>56.49748810257361</v>
+        <v>56.29713666309858</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1123303366760903</v>
+        <v>0.1134128868076606</v>
       </c>
       <c r="T45">
-        <v>1.536497382819636</v>
+        <v>1.561498540592624</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.657828287687574</v>
+        <v>3.574695826603766</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08654530461228996</v>
+        <v>0.08762777131920846</v>
       </c>
       <c r="C46">
-        <v>206.5371974172584</v>
+        <v>194.3140575190023</v>
       </c>
       <c r="D46">
-        <v>324.4312692049768</v>
+        <v>316.0352673018961</v>
       </c>
       <c r="E46">
-        <v>133.9802722701766</v>
+        <v>137.807410265352</v>
       </c>
       <c r="F46">
-        <v>168.3940717877184</v>
+        <v>172.2212097828939</v>
       </c>
       <c r="G46">
         <v>50.5</v>
@@ -5041,45 +5041,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M46">
-        <v>10.32255660058714</v>
+        <v>11.0393795470835</v>
       </c>
       <c r="N46">
-        <v>26.57744339941286</v>
+        <v>25.86062045291651</v>
       </c>
       <c r="O46">
-        <v>3.880306736314278</v>
+        <v>3.77565058612581</v>
       </c>
       <c r="P46">
-        <v>22.69713666309859</v>
+        <v>22.0849698667907</v>
       </c>
       <c r="Q46">
-        <v>56.29713666309858</v>
+        <v>55.68496986679069</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1134128868076606</v>
+        <v>0.1145348023985608</v>
       </c>
       <c r="T46">
-        <v>1.561498540592624</v>
+        <v>1.587408831375538</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.574695826603766</v>
+        <v>3.342579158785119</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08762777131920846</v>
+        <v>0.08765811002612696</v>
       </c>
       <c r="C47">
-        <v>194.3140575190023</v>
+        <v>190.2578575488692</v>
       </c>
       <c r="D47">
-        <v>316.0352673018961</v>
+        <v>315.8062053269384</v>
       </c>
       <c r="E47">
-        <v>137.807410265352</v>
+        <v>141.6345482605274</v>
       </c>
       <c r="F47">
-        <v>172.2212097828939</v>
+        <v>176.0483477780693</v>
       </c>
       <c r="G47">
         <v>50.5</v>
@@ -5123,28 +5123,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M47">
-        <v>11.0393795470835</v>
+        <v>11.28469909257424</v>
       </c>
       <c r="N47">
-        <v>25.86062045291651</v>
+        <v>25.61530090742577</v>
       </c>
       <c r="O47">
-        <v>3.77565058612581</v>
+        <v>3.739833932484161</v>
       </c>
       <c r="P47">
-        <v>22.0849698667907</v>
+        <v>21.87546697494161</v>
       </c>
       <c r="Q47">
-        <v>55.68496986679069</v>
+        <v>55.4754669749416</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1145348023985608</v>
+        <v>0.1156982704187536</v>
       </c>
       <c r="T47">
-        <v>1.587408831375538</v>
+        <v>1.61427876255782</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.342579158785119</v>
+        <v>3.269914394463704</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08765811002612696</v>
+        <v>0.08768844873304546</v>
       </c>
       <c r="C48">
-        <v>190.2578575488692</v>
+        <v>186.2019893859207</v>
       </c>
       <c r="D48">
-        <v>315.8062053269384</v>
+        <v>315.5774751591654</v>
       </c>
       <c r="E48">
-        <v>141.6345482605274</v>
+        <v>145.4616862557028</v>
       </c>
       <c r="F48">
-        <v>176.0483477780693</v>
+        <v>179.8754857732447</v>
       </c>
       <c r="G48">
         <v>50.5</v>
@@ -5205,28 +5205,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M48">
-        <v>11.28469909257424</v>
+        <v>11.53001863806499</v>
       </c>
       <c r="N48">
-        <v>25.61530090742577</v>
+        <v>25.36998136193502</v>
       </c>
       <c r="O48">
-        <v>3.739833932484161</v>
+        <v>3.704017278842513</v>
       </c>
       <c r="P48">
-        <v>21.87546697494161</v>
+        <v>21.6659640830925</v>
       </c>
       <c r="Q48">
-        <v>55.4754669749416</v>
+        <v>55.2659640830925</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1156982704187536</v>
+        <v>0.1169056428925386</v>
       </c>
       <c r="T48">
-        <v>1.61427876255782</v>
+        <v>1.642162653407358</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.269914394463704</v>
+        <v>3.200341747772986</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08768844873304546</v>
+        <v>0.08771878743996396</v>
       </c>
       <c r="C49">
-        <v>186.2019893859207</v>
+        <v>182.1464523097212</v>
       </c>
       <c r="D49">
-        <v>315.5774751591654</v>
+        <v>315.3490760781413</v>
       </c>
       <c r="E49">
-        <v>145.4616862557028</v>
+        <v>149.2888242508783</v>
       </c>
       <c r="F49">
-        <v>179.8754857732447</v>
+        <v>183.7026237684201</v>
       </c>
       <c r="G49">
         <v>50.5</v>
@@ -5287,28 +5287,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M49">
-        <v>11.53001863806499</v>
+        <v>11.77533818355573</v>
       </c>
       <c r="N49">
-        <v>25.36998136193502</v>
+        <v>25.12466181644427</v>
       </c>
       <c r="O49">
-        <v>3.704017278842513</v>
+        <v>3.668200625200864</v>
       </c>
       <c r="P49">
-        <v>21.6659640830925</v>
+        <v>21.45646119124341</v>
       </c>
       <c r="Q49">
-        <v>55.2659640830925</v>
+        <v>55.0564611912434</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1169056428925386</v>
+        <v>0.1181594527691615</v>
       </c>
       <c r="T49">
-        <v>1.642162653407358</v>
+        <v>1.671119001597262</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.200341747772986</v>
+        <v>3.133667961361049</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08771878743996396</v>
+        <v>0.08774912614688246</v>
       </c>
       <c r="C50">
-        <v>182.1464523097212</v>
+        <v>178.0912456019186</v>
       </c>
       <c r="D50">
-        <v>315.3490760781413</v>
+        <v>315.1210073655141</v>
       </c>
       <c r="E50">
-        <v>149.2888242508782</v>
+        <v>153.1159622460536</v>
       </c>
       <c r="F50">
-        <v>183.7026237684201</v>
+        <v>187.5297617635955</v>
       </c>
       <c r="G50">
         <v>50.5</v>
@@ -5369,28 +5369,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M50">
-        <v>11.77533818355573</v>
+        <v>12.02065772904647</v>
       </c>
       <c r="N50">
-        <v>25.12466181644428</v>
+        <v>24.87934227095353</v>
       </c>
       <c r="O50">
-        <v>3.668200625200864</v>
+        <v>3.632383971559216</v>
       </c>
       <c r="P50">
-        <v>21.45646119124341</v>
+        <v>21.24695829939432</v>
       </c>
       <c r="Q50">
-        <v>55.05646119124341</v>
+        <v>54.84695829939432</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1181594527691615</v>
+        <v>0.1194624316605538</v>
       </c>
       <c r="T50">
-        <v>1.671119001597262</v>
+        <v>1.701210892853437</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.13366796136105</v>
+        <v>3.069715553986335</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08774912614688246</v>
+        <v>0.08777946485380096</v>
       </c>
       <c r="C51">
-        <v>178.0912456019186</v>
+        <v>174.0363685462378</v>
       </c>
       <c r="D51">
-        <v>315.1210073655141</v>
+        <v>314.8932683050087</v>
       </c>
       <c r="E51">
-        <v>153.1159622460536</v>
+        <v>156.9431002412291</v>
       </c>
       <c r="F51">
-        <v>187.5297617635955</v>
+        <v>191.3568997587709</v>
       </c>
       <c r="G51">
         <v>50.5</v>
@@ -5451,28 +5451,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M51">
-        <v>12.02065772904647</v>
+        <v>12.26597727453722</v>
       </c>
       <c r="N51">
-        <v>24.87934227095353</v>
+        <v>24.63402272546279</v>
       </c>
       <c r="O51">
-        <v>3.632383971559216</v>
+        <v>3.596567317917567</v>
       </c>
       <c r="P51">
-        <v>21.24695829939432</v>
+        <v>21.03745540754522</v>
       </c>
       <c r="Q51">
-        <v>54.84695829939432</v>
+        <v>54.63745540754522</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1194624316605538</v>
+        <v>0.1208175297076019</v>
       </c>
       <c r="T51">
-        <v>1.701210892853437</v>
+        <v>1.732506459759859</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.069715553986335</v>
+        <v>3.008321242906608</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08777946485380096</v>
+        <v>0.09120701556071947</v>
       </c>
       <c r="C52">
-        <v>174.0363685462378</v>
+        <v>146.4394973709676</v>
       </c>
       <c r="D52">
-        <v>314.8932683050087</v>
+        <v>291.1235351249139</v>
       </c>
       <c r="E52">
-        <v>156.9431002412291</v>
+        <v>160.7702382364045</v>
       </c>
       <c r="F52">
-        <v>191.3568997587709</v>
+        <v>195.1840377539464</v>
       </c>
       <c r="G52">
         <v>50.5</v>
@@ -5533,45 +5533,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M52">
-        <v>12.26597727453722</v>
+        <v>14.03373231450874</v>
       </c>
       <c r="N52">
-        <v>24.63402272546279</v>
+        <v>22.86626768549126</v>
       </c>
       <c r="O52">
-        <v>3.596567317917567</v>
+        <v>3.338475082081723</v>
       </c>
       <c r="P52">
-        <v>21.03745540754522</v>
+        <v>19.52779260340954</v>
       </c>
       <c r="Q52">
-        <v>54.63745540754522</v>
+        <v>53.12779260340953</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1208175297076019</v>
+        <v>0.1222279378790193</v>
       </c>
       <c r="T52">
-        <v>1.732506459759859</v>
+        <v>1.765079396744095</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.008321242906608</v>
+        <v>2.629378925936261</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09120701556071947</v>
+        <v>0.09130396626763795</v>
       </c>
       <c r="C53">
-        <v>146.4394973709676</v>
+        <v>141.99209185087</v>
       </c>
       <c r="D53">
-        <v>291.1235351249139</v>
+        <v>290.5032675999918</v>
       </c>
       <c r="E53">
-        <v>160.7702382364045</v>
+        <v>164.5973762315799</v>
       </c>
       <c r="F53">
-        <v>195.1840377539464</v>
+        <v>199.0111757491218</v>
       </c>
       <c r="G53">
         <v>50.5</v>
@@ -5615,28 +5615,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M53">
-        <v>14.03373231450874</v>
+        <v>14.30890353636186</v>
       </c>
       <c r="N53">
-        <v>22.86626768549126</v>
+        <v>22.59109646363815</v>
       </c>
       <c r="O53">
-        <v>3.338475082081723</v>
+        <v>3.298300083691169</v>
       </c>
       <c r="P53">
-        <v>19.52779260340954</v>
+        <v>19.29279637994698</v>
       </c>
       <c r="Q53">
-        <v>53.12779260340953</v>
+        <v>52.89279637994697</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1222279378790193</v>
+        <v>0.1236971130575791</v>
       </c>
       <c r="T53">
-        <v>1.765079396744095</v>
+        <v>1.799009539436006</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.629378925936261</v>
+        <v>2.578813946591334</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09130396626763795</v>
+        <v>0.09140091697455646</v>
       </c>
       <c r="C54">
-        <v>141.99209185087</v>
+        <v>137.5473237941835</v>
       </c>
       <c r="D54">
-        <v>290.5032675999918</v>
+        <v>289.8856375384808</v>
       </c>
       <c r="E54">
-        <v>164.5973762315799</v>
+        <v>168.4245142267554</v>
       </c>
       <c r="F54">
-        <v>199.0111757491218</v>
+        <v>202.8383137442972</v>
       </c>
       <c r="G54">
         <v>50.5</v>
@@ -5697,28 +5697,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M54">
-        <v>14.30890353636186</v>
+        <v>14.58407475821497</v>
       </c>
       <c r="N54">
-        <v>22.59109646363815</v>
+        <v>22.31592524178503</v>
       </c>
       <c r="O54">
-        <v>3.298300083691169</v>
+        <v>3.258125085300615</v>
       </c>
       <c r="P54">
-        <v>19.29279637994698</v>
+        <v>19.05780015648442</v>
       </c>
       <c r="Q54">
-        <v>52.89279637994697</v>
+        <v>52.65780015648441</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1236971130575791</v>
+        <v>0.1252288063288435</v>
       </c>
       <c r="T54">
-        <v>1.799009539436006</v>
+        <v>1.834383517987149</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.578813946591334</v>
+        <v>2.530157079674515</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09140091697455646</v>
+        <v>0.09329639168147497</v>
       </c>
       <c r="C55">
-        <v>137.5473237941835</v>
+        <v>122.1514986966688</v>
       </c>
       <c r="D55">
-        <v>289.8856375384808</v>
+        <v>278.3169504361414</v>
       </c>
       <c r="E55">
-        <v>168.4245142267554</v>
+        <v>172.2516522219308</v>
       </c>
       <c r="F55">
-        <v>202.8383137442972</v>
+        <v>206.6654517394726</v>
       </c>
       <c r="G55">
         <v>50.5</v>
@@ -5779,45 +5779,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M55">
-        <v>14.58407475821497</v>
+        <v>15.66524124185203</v>
       </c>
       <c r="N55">
-        <v>22.31592524178503</v>
+        <v>21.23475875814798</v>
       </c>
       <c r="O55">
-        <v>3.258125085300615</v>
+        <v>3.100274778689605</v>
       </c>
       <c r="P55">
-        <v>19.05780015648442</v>
+        <v>18.13448397945837</v>
       </c>
       <c r="Q55">
-        <v>52.65780015648441</v>
+        <v>51.73448397945837</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1252288063288435</v>
+        <v>0.1268270949597282</v>
       </c>
       <c r="T55">
-        <v>1.834383517987149</v>
+        <v>1.871295495605731</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.146</v>
       </c>
       <c r="W55">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.530157079674515</v>
+        <v>2.355533466118361</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09329639168147497</v>
+        <v>0.09342664838839347</v>
       </c>
       <c r="C56">
-        <v>122.1514986966688</v>
+        <v>117.5631765604685</v>
       </c>
       <c r="D56">
-        <v>278.3169504361414</v>
+        <v>277.5557662951165</v>
       </c>
       <c r="E56">
-        <v>172.2516522219308</v>
+        <v>176.0787902171062</v>
       </c>
       <c r="F56">
-        <v>206.6654517394726</v>
+        <v>210.492589734648</v>
       </c>
       <c r="G56">
         <v>50.5</v>
@@ -5861,28 +5861,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M56">
-        <v>15.66524124185203</v>
+        <v>15.95533830188632</v>
       </c>
       <c r="N56">
-        <v>21.23475875814798</v>
+        <v>20.94466169811368</v>
       </c>
       <c r="O56">
-        <v>3.100274778689605</v>
+        <v>3.057920607924598</v>
       </c>
       <c r="P56">
-        <v>18.13448397945837</v>
+        <v>17.88674109018909</v>
       </c>
       <c r="Q56">
-        <v>51.73448397945837</v>
+        <v>51.48674109018908</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1268270949597282</v>
+        <v>0.1284964186408744</v>
       </c>
       <c r="T56">
-        <v>1.871295495605731</v>
+        <v>1.909848005562919</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.355533466118361</v>
+        <v>2.312705584916209</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09342664838839347</v>
+        <v>0.09355690509531198</v>
       </c>
       <c r="C57">
-        <v>117.5631765604685</v>
+        <v>112.979006675733</v>
       </c>
       <c r="D57">
-        <v>277.5557662951165</v>
+        <v>276.7987344055565</v>
       </c>
       <c r="E57">
-        <v>176.0787902171062</v>
+        <v>179.9059282122816</v>
       </c>
       <c r="F57">
-        <v>210.492589734648</v>
+        <v>214.3197277298235</v>
       </c>
       <c r="G57">
         <v>50.5</v>
@@ -5943,28 +5943,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M57">
-        <v>15.95533830188632</v>
+        <v>16.24543536192062</v>
       </c>
       <c r="N57">
-        <v>20.94466169811368</v>
+        <v>20.65456463807939</v>
       </c>
       <c r="O57">
-        <v>3.057920607924598</v>
+        <v>3.01556643715959</v>
       </c>
       <c r="P57">
-        <v>17.88674109018909</v>
+        <v>17.63899820091979</v>
       </c>
       <c r="Q57">
-        <v>51.48674109018908</v>
+        <v>51.23899820091979</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1284964186408744</v>
+        <v>0.1302416206711636</v>
       </c>
       <c r="T57">
-        <v>1.909848005562919</v>
+        <v>1.950152902336341</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.312705584916209</v>
+        <v>2.271407270899848</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09355690509531198</v>
+        <v>0.09368716180223047</v>
       </c>
       <c r="C58">
-        <v>112.979006675733</v>
+        <v>108.3989551591471</v>
       </c>
       <c r="D58">
-        <v>276.7987344055565</v>
+        <v>276.045820884146</v>
       </c>
       <c r="E58">
-        <v>179.9059282122816</v>
+        <v>183.7330662074571</v>
       </c>
       <c r="F58">
-        <v>214.3197277298235</v>
+        <v>218.1468657249989</v>
       </c>
       <c r="G58">
         <v>50.5</v>
@@ -6025,28 +6025,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M58">
-        <v>16.24543536192062</v>
+        <v>16.53553242195492</v>
       </c>
       <c r="N58">
-        <v>20.65456463807939</v>
+        <v>20.36446757804509</v>
       </c>
       <c r="O58">
-        <v>3.01556643715959</v>
+        <v>2.973212266394583</v>
       </c>
       <c r="P58">
-        <v>17.63899820091979</v>
+        <v>17.3912553116505</v>
       </c>
       <c r="Q58">
-        <v>51.23899820091979</v>
+        <v>50.9912553116505</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1302416206711636</v>
+        <v>0.1320679948889081</v>
       </c>
       <c r="T58">
-        <v>1.950152902336341</v>
+        <v>1.992332445471318</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.271407270899848</v>
+        <v>2.231558020533184</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09368716180223047</v>
+        <v>0.09381741850914897</v>
       </c>
       <c r="C59">
-        <v>108.3989551591471</v>
+        <v>103.8229884950557</v>
       </c>
       <c r="D59">
-        <v>276.045820884146</v>
+        <v>275.29699221523</v>
       </c>
       <c r="E59">
-        <v>183.7330662074571</v>
+        <v>187.5602042026325</v>
       </c>
       <c r="F59">
-        <v>218.1468657249989</v>
+        <v>221.9740037201743</v>
       </c>
       <c r="G59">
         <v>50.5</v>
@@ -6107,28 +6107,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M59">
-        <v>16.53553242195492</v>
+        <v>16.82562948198921</v>
       </c>
       <c r="N59">
-        <v>20.36446757804509</v>
+        <v>20.07437051801079</v>
       </c>
       <c r="O59">
-        <v>2.973212266394583</v>
+        <v>2.930858095629576</v>
       </c>
       <c r="P59">
-        <v>17.3912553116505</v>
+        <v>17.14351242238122</v>
       </c>
       <c r="Q59">
-        <v>50.9912553116505</v>
+        <v>50.74351242238122</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1320679948889081</v>
+        <v>0.1339813393074976</v>
       </c>
       <c r="T59">
-        <v>1.992332445471318</v>
+        <v>2.036520538279389</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.231558020533184</v>
+        <v>2.193082882248129</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09381741850914896</v>
+        <v>0.09394767521606748</v>
       </c>
       <c r="C60">
-        <v>103.8229884950558</v>
+        <v>99.25107353049182</v>
       </c>
       <c r="D60">
-        <v>275.2969922152301</v>
+        <v>274.5522152458415</v>
       </c>
       <c r="E60">
-        <v>187.5602042026324</v>
+        <v>191.3873421978079</v>
       </c>
       <c r="F60">
-        <v>221.9740037201743</v>
+        <v>225.8011417153497</v>
       </c>
       <c r="G60">
         <v>50.5</v>
@@ -6189,28 +6189,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M60">
-        <v>16.82562948198921</v>
+        <v>17.11572654202351</v>
       </c>
       <c r="N60">
-        <v>20.0743705180108</v>
+        <v>19.7842734579765</v>
       </c>
       <c r="O60">
-        <v>2.930858095629576</v>
+        <v>2.888503924864569</v>
       </c>
       <c r="P60">
-        <v>17.14351242238122</v>
+        <v>16.89576953311193</v>
       </c>
       <c r="Q60">
-        <v>50.74351242238122</v>
+        <v>50.49576953311193</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1339813393074975</v>
+        <v>0.1359880176001646</v>
       </c>
       <c r="T60">
-        <v>2.036520538279389</v>
+        <v>2.082864147809805</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.19308288224813</v>
+        <v>2.15591198593884</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09394767521606748</v>
+        <v>0.09407793192298597</v>
       </c>
       <c r="C61">
-        <v>99.25107353049182</v>
+        <v>94.68317747028274</v>
       </c>
       <c r="D61">
-        <v>274.5522152458415</v>
+        <v>273.8114571808078</v>
       </c>
       <c r="E61">
-        <v>191.3873421978079</v>
+        <v>195.2144801929833</v>
       </c>
       <c r="F61">
-        <v>225.8011417153497</v>
+        <v>229.6282797105251</v>
       </c>
       <c r="G61">
         <v>50.5</v>
@@ -6271,28 +6271,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M61">
-        <v>17.11572654202351</v>
+        <v>17.4058236020578</v>
       </c>
       <c r="N61">
-        <v>19.7842734579765</v>
+        <v>19.4941763979422</v>
       </c>
       <c r="O61">
-        <v>2.888503924864569</v>
+        <v>2.846149754099561</v>
       </c>
       <c r="P61">
-        <v>16.89576953311193</v>
+        <v>16.64802664384264</v>
       </c>
       <c r="Q61">
-        <v>50.49576953311193</v>
+        <v>50.24802664384264</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1359880176001646</v>
+        <v>0.1380950298074649</v>
       </c>
       <c r="T61">
-        <v>2.082864147809805</v>
+        <v>2.131524937816741</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.15591198593884</v>
+        <v>2.119980119506526</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09407793192298597</v>
+        <v>0.09420818862990449</v>
       </c>
       <c r="C62">
-        <v>94.68317747028274</v>
+        <v>90.11926787223638</v>
       </c>
       <c r="D62">
-        <v>273.8114571808078</v>
+        <v>273.0746855779369</v>
       </c>
       <c r="E62">
-        <v>195.2144801929833</v>
+        <v>199.0416181881587</v>
       </c>
       <c r="F62">
-        <v>229.6282797105251</v>
+        <v>233.4554177057005</v>
       </c>
       <c r="G62">
         <v>50.5</v>
@@ -6353,28 +6353,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M62">
-        <v>17.4058236020578</v>
+        <v>17.6959206620921</v>
       </c>
       <c r="N62">
-        <v>19.4941763979422</v>
+        <v>19.2040793379079</v>
       </c>
       <c r="O62">
-        <v>2.846149754099561</v>
+        <v>2.803795583334554</v>
       </c>
       <c r="P62">
-        <v>16.64802664384264</v>
+        <v>16.40028375457335</v>
       </c>
       <c r="Q62">
-        <v>50.24802664384264</v>
+        <v>50.00028375457335</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1380950298074649</v>
+        <v>0.140310093922832</v>
       </c>
       <c r="T62">
-        <v>2.131524937816741</v>
+        <v>2.18268115295224</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.119980119506526</v>
+        <v>2.085226347055599</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09420818862990449</v>
+        <v>0.09433844533682298</v>
       </c>
       <c r="C63">
-        <v>90.11926787223638</v>
+        <v>85.55931264240593</v>
       </c>
       <c r="D63">
-        <v>273.0746855779369</v>
+        <v>272.3418683432819</v>
       </c>
       <c r="E63">
-        <v>199.0416181881587</v>
+        <v>202.8687561833341</v>
       </c>
       <c r="F63">
-        <v>233.4554177057005</v>
+        <v>237.2825557008759</v>
       </c>
       <c r="G63">
         <v>50.5</v>
@@ -6435,28 +6435,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M63">
-        <v>17.6959206620921</v>
+        <v>17.9860177221264</v>
       </c>
       <c r="N63">
-        <v>19.2040793379079</v>
+        <v>18.91398227787361</v>
       </c>
       <c r="O63">
-        <v>2.803795583334554</v>
+        <v>2.761441412569547</v>
       </c>
       <c r="P63">
-        <v>16.40028375457335</v>
+        <v>16.15254086530406</v>
       </c>
       <c r="Q63">
-        <v>50.00028375457335</v>
+        <v>49.75254086530406</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.140310093922832</v>
+        <v>0.1426417403600605</v>
       </c>
       <c r="T63">
-        <v>2.18268115295224</v>
+        <v>2.23652980046329</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.085226347055599</v>
+        <v>2.051593664038573</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09433844533682298</v>
+        <v>0.09446870204374147</v>
       </c>
       <c r="C64">
-        <v>85.55931264240593</v>
+        <v>81.0032800304285</v>
       </c>
       <c r="D64">
-        <v>272.3418683432819</v>
+        <v>271.6129737264799</v>
       </c>
       <c r="E64">
-        <v>202.8687561833341</v>
+        <v>206.6958941785095</v>
       </c>
       <c r="F64">
-        <v>237.2825557008759</v>
+        <v>241.1096936960514</v>
       </c>
       <c r="G64">
         <v>50.5</v>
@@ -6517,28 +6517,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M64">
-        <v>17.9860177221264</v>
+        <v>18.2761147821607</v>
       </c>
       <c r="N64">
-        <v>18.91398227787361</v>
+        <v>18.62388521783931</v>
       </c>
       <c r="O64">
-        <v>2.761441412569547</v>
+        <v>2.719087241804539</v>
       </c>
       <c r="P64">
-        <v>16.15254086530406</v>
+        <v>15.90479797603477</v>
       </c>
       <c r="Q64">
-        <v>49.75254086530406</v>
+        <v>49.50479797603477</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1426417403600605</v>
+        <v>0.1450994217398418</v>
       </c>
       <c r="T64">
-        <v>2.23652980046329</v>
+        <v>2.29328918567764</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.051593664038573</v>
+        <v>2.01902868524431</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09446870204374147</v>
+        <v>0.10236011075066</v>
       </c>
       <c r="C65">
-        <v>81.0032800304285</v>
+        <v>39.28001776445393</v>
       </c>
       <c r="D65">
-        <v>271.6129737264799</v>
+        <v>233.7168494556807</v>
       </c>
       <c r="E65">
-        <v>206.6958941785095</v>
+        <v>210.523032173685</v>
       </c>
       <c r="F65">
-        <v>241.1096936960514</v>
+        <v>244.9368316912268</v>
       </c>
       <c r="G65">
         <v>50.5</v>
@@ -6599,45 +6599,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M65">
-        <v>18.2761147821607</v>
+        <v>22.04431485221041</v>
       </c>
       <c r="N65">
-        <v>18.62388521783931</v>
+        <v>14.85568514778959</v>
       </c>
       <c r="O65">
-        <v>2.719087241804539</v>
+        <v>2.16893003157728</v>
       </c>
       <c r="P65">
-        <v>15.90479797603477</v>
+        <v>12.68675511621231</v>
       </c>
       <c r="Q65">
-        <v>49.50479797603477</v>
+        <v>46.2867551162123</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1450994217398418</v>
+        <v>0.1476936409740555</v>
       </c>
       <c r="T65">
-        <v>2.29328918567764</v>
+        <v>2.353201870070566</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.146</v>
       </c>
       <c r="W65">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.01902868524431</v>
+        <v>1.673900969360361</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.10236011075066</v>
+        <v>0.1026116354575785</v>
       </c>
       <c r="C66">
-        <v>39.28001776445393</v>
+        <v>34.41813465786288</v>
       </c>
       <c r="D66">
-        <v>233.7168494556807</v>
+        <v>232.6821043442651</v>
       </c>
       <c r="E66">
-        <v>210.523032173685</v>
+        <v>214.3501701688604</v>
       </c>
       <c r="F66">
-        <v>244.9368316912268</v>
+        <v>248.7639696864022</v>
       </c>
       <c r="G66">
         <v>50.5</v>
@@ -6681,28 +6681,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M66">
-        <v>22.04431485221041</v>
+        <v>22.3887572717762</v>
       </c>
       <c r="N66">
-        <v>14.85568514778959</v>
+        <v>14.51124272822381</v>
       </c>
       <c r="O66">
-        <v>2.16893003157728</v>
+        <v>2.118641438320676</v>
       </c>
       <c r="P66">
-        <v>12.68675511621231</v>
+        <v>12.39260128990313</v>
       </c>
       <c r="Q66">
-        <v>46.2867551162123</v>
+        <v>45.99260128990312</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1476936409740555</v>
+        <v>0.1504361013073671</v>
       </c>
       <c r="T66">
-        <v>2.353201870070566</v>
+        <v>2.416538136428801</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.673900969360361</v>
+        <v>1.648148646754817</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1026116354575785</v>
+        <v>0.102863160164497</v>
       </c>
       <c r="C67">
-        <v>34.41813465786288</v>
+        <v>29.56537351227567</v>
       </c>
       <c r="D67">
-        <v>232.6821043442651</v>
+        <v>231.6564811938533</v>
       </c>
       <c r="E67">
-        <v>214.3501701688604</v>
+        <v>218.1773081640358</v>
       </c>
       <c r="F67">
-        <v>248.7639696864022</v>
+        <v>252.5911076815777</v>
       </c>
       <c r="G67">
         <v>50.5</v>
@@ -6763,28 +6763,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M67">
-        <v>22.3887572717762</v>
+        <v>22.73319969134199</v>
       </c>
       <c r="N67">
-        <v>14.51124272822381</v>
+        <v>14.16680030865802</v>
       </c>
       <c r="O67">
-        <v>2.118641438320676</v>
+        <v>2.068352845064071</v>
       </c>
       <c r="P67">
-        <v>12.39260128990313</v>
+        <v>12.09844746359395</v>
       </c>
       <c r="Q67">
-        <v>45.99260128990312</v>
+        <v>45.69844746359394</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1504361013073671</v>
+        <v>0.1533398828367558</v>
       </c>
       <c r="T67">
-        <v>2.416538136428801</v>
+        <v>2.483600065513991</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.648148646754817</v>
+        <v>1.623176697561562</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.102863160164497</v>
+        <v>0.1031146848714155</v>
       </c>
       <c r="C68">
-        <v>29.56537351227567</v>
+        <v>24.72161423289037</v>
       </c>
       <c r="D68">
-        <v>231.6564811938533</v>
+        <v>230.6398599096435</v>
       </c>
       <c r="E68">
-        <v>218.1773081640358</v>
+        <v>222.0044461592112</v>
       </c>
       <c r="F68">
-        <v>252.5911076815777</v>
+        <v>256.4182456767531</v>
       </c>
       <c r="G68">
         <v>50.5</v>
@@ -6845,28 +6845,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M68">
-        <v>22.73319969134199</v>
+        <v>23.07764211090778</v>
       </c>
       <c r="N68">
-        <v>14.16680030865802</v>
+        <v>13.82235788909223</v>
       </c>
       <c r="O68">
-        <v>2.068352845064071</v>
+        <v>2.018064251807465</v>
       </c>
       <c r="P68">
-        <v>12.09844746359395</v>
+        <v>11.80429363728476</v>
       </c>
       <c r="Q68">
-        <v>45.69844746359394</v>
+        <v>45.40429363728476</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1533398828367558</v>
+        <v>0.1564196511255015</v>
       </c>
       <c r="T68">
-        <v>2.483600065513991</v>
+        <v>2.554726353937678</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.623176697561562</v>
+        <v>1.598950179687509</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1031146848714155</v>
+        <v>0.103366209578334</v>
       </c>
       <c r="C69">
-        <v>24.72161423289037</v>
+        <v>19.88673882383227</v>
       </c>
       <c r="D69">
-        <v>230.6398599096435</v>
+        <v>229.6321224957608</v>
       </c>
       <c r="E69">
-        <v>222.0044461592112</v>
+        <v>225.8315841543866</v>
       </c>
       <c r="F69">
-        <v>256.4182456767531</v>
+        <v>260.2453836719285</v>
       </c>
       <c r="G69">
         <v>50.5</v>
@@ -6927,28 +6927,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M69">
-        <v>23.07764211090778</v>
+        <v>23.42208453047356</v>
       </c>
       <c r="N69">
-        <v>13.82235788909223</v>
+        <v>13.47791546952644</v>
       </c>
       <c r="O69">
-        <v>2.018064251807465</v>
+        <v>1.967775658550861</v>
       </c>
       <c r="P69">
-        <v>11.80429363728476</v>
+        <v>11.51013981097558</v>
       </c>
       <c r="Q69">
-        <v>45.40429363728476</v>
+        <v>45.11013981097557</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1564196511255015</v>
+        <v>0.1596919049322937</v>
       </c>
       <c r="T69">
-        <v>2.554726353937678</v>
+        <v>2.630298035387845</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.598950179687509</v>
+        <v>1.57543620645681</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.103366209578334</v>
+        <v>0.1036177342852525</v>
       </c>
       <c r="C70">
-        <v>19.88673882383227</v>
+        <v>15.06063134249786</v>
       </c>
       <c r="D70">
-        <v>229.6321224957608</v>
+        <v>228.6331530096018</v>
       </c>
       <c r="E70">
-        <v>225.8315841543866</v>
+        <v>229.658722149562</v>
       </c>
       <c r="F70">
-        <v>260.2453836719285</v>
+        <v>264.0725216671039</v>
       </c>
       <c r="G70">
         <v>50.5</v>
@@ -7009,28 +7009,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M70">
-        <v>23.42208453047356</v>
+        <v>23.76652695003935</v>
       </c>
       <c r="N70">
-        <v>13.47791546952644</v>
+        <v>13.13347304996066</v>
       </c>
       <c r="O70">
-        <v>1.967775658550861</v>
+        <v>1.917487065294256</v>
       </c>
       <c r="P70">
-        <v>11.51013981097558</v>
+        <v>11.2159859846664</v>
       </c>
       <c r="Q70">
-        <v>45.11013981097557</v>
+        <v>44.8159859846664</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1596919049322937</v>
+        <v>0.1631752718879113</v>
       </c>
       <c r="T70">
-        <v>2.630298035387845</v>
+        <v>2.710745309189636</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.57543620645681</v>
+        <v>1.552603797667581</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1036177342852525</v>
+        <v>0.103869258992171</v>
       </c>
       <c r="C71">
-        <v>15.06063134249786</v>
+        <v>10.24317785508674</v>
       </c>
       <c r="D71">
-        <v>228.6331530096018</v>
+        <v>227.6428375173661</v>
       </c>
       <c r="E71">
-        <v>229.658722149562</v>
+        <v>233.4858601447375</v>
       </c>
       <c r="F71">
-        <v>264.0725216671039</v>
+        <v>267.8996596622794</v>
       </c>
       <c r="G71">
         <v>50.5</v>
@@ -7091,28 +7091,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M71">
-        <v>23.76652695003935</v>
+        <v>24.11096936960514</v>
       </c>
       <c r="N71">
-        <v>13.13347304996066</v>
+        <v>12.78903063039487</v>
       </c>
       <c r="O71">
-        <v>1.917487065294256</v>
+        <v>1.86719847203765</v>
       </c>
       <c r="P71">
-        <v>11.2159859846664</v>
+        <v>10.92183215835722</v>
       </c>
       <c r="Q71">
-        <v>44.8159859846664</v>
+        <v>44.52183215835721</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1631752718879113</v>
+        <v>0.1668908633072366</v>
       </c>
       <c r="T71">
-        <v>2.710745309189636</v>
+        <v>2.796555734578213</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.552603797667581</v>
+        <v>1.530423743415187</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.103869258992171</v>
+        <v>0.1041207836990895</v>
       </c>
       <c r="C72">
-        <v>10.24317785508674</v>
+        <v>5.434266393284418</v>
       </c>
       <c r="D72">
-        <v>227.6428375173661</v>
+        <v>226.6610640507392</v>
       </c>
       <c r="E72">
-        <v>233.4858601447375</v>
+        <v>237.3129981399129</v>
       </c>
       <c r="F72">
-        <v>267.8996596622794</v>
+        <v>271.7267976574548</v>
       </c>
       <c r="G72">
         <v>50.5</v>
@@ -7173,28 +7173,28 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M72">
-        <v>24.11096936960514</v>
+        <v>24.45541178917093</v>
       </c>
       <c r="N72">
-        <v>12.78903063039487</v>
+        <v>12.44458821082908</v>
       </c>
       <c r="O72">
-        <v>1.86719847203765</v>
+        <v>1.816909878781045</v>
       </c>
       <c r="P72">
-        <v>10.92183215835722</v>
+        <v>10.62767833204803</v>
       </c>
       <c r="Q72">
-        <v>44.52183215835721</v>
+        <v>44.22767833204803</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1668908633072366</v>
+        <v>0.1708627024106534</v>
       </c>
       <c r="T72">
-        <v>2.796555734578213</v>
+        <v>2.888284120338416</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.530423743415187</v>
+        <v>1.508868479423424</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1041207836990895</v>
+        <v>0.1410256888066708</v>
       </c>
       <c r="C73">
-        <v>5.434266393284474</v>
+        <v>-86.23581781946618</v>
       </c>
       <c r="D73">
-        <v>226.6610640507392</v>
+        <v>138.8181178331639</v>
       </c>
       <c r="E73">
-        <v>237.3129981399128</v>
+        <v>241.1401361350883</v>
       </c>
       <c r="F73">
-        <v>271.7267976574547</v>
+        <v>275.5539356526301</v>
       </c>
       <c r="G73">
         <v>50.5</v>
@@ -7255,45 +7255,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M73">
-        <v>24.45541178917092</v>
+        <v>40.4513177538061</v>
       </c>
       <c r="N73">
-        <v>12.44458821082908</v>
+        <v>-3.551317753806096</v>
       </c>
       <c r="O73">
-        <v>1.816909878781046</v>
+        <v>-0.51849239205569</v>
       </c>
       <c r="P73">
-        <v>10.62767833204804</v>
+        <v>-3.032825361750406</v>
       </c>
       <c r="Q73">
-        <v>44.22767833204803</v>
+        <v>30.56717463824959</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1708627024106534</v>
+        <v>0.1764518799950132</v>
       </c>
       <c r="T73">
-        <v>2.888284120338415</v>
+        <v>3.017364434064969</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.146</v>
+        <v>0.1331823114586445</v>
       </c>
       <c r="W73">
-        <v>0.07686</v>
+        <v>0.127248836677871</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.508868479423424</v>
+        <v>0.9122076127304419</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1410256888066708</v>
+        <v>0.1420356888066708</v>
       </c>
       <c r="C74">
-        <v>-86.23581781946618</v>
+        <v>-91.51986125949338</v>
       </c>
       <c r="D74">
-        <v>138.8181178331639</v>
+        <v>137.3612123883122</v>
       </c>
       <c r="E74">
-        <v>241.1401361350883</v>
+        <v>244.9672741302637</v>
       </c>
       <c r="F74">
-        <v>275.5539356526301</v>
+        <v>279.3810736478056</v>
       </c>
       <c r="G74">
         <v>50.5</v>
@@ -7337,37 +7337,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M74">
-        <v>40.4513177538061</v>
+        <v>41.01314161149786</v>
       </c>
       <c r="N74">
-        <v>-3.551317753806096</v>
+        <v>-4.113141611497859</v>
       </c>
       <c r="O74">
-        <v>-0.51849239205569</v>
+        <v>-0.6005186752786874</v>
       </c>
       <c r="P74">
-        <v>-3.032825361750406</v>
+        <v>-3.512622936219172</v>
       </c>
       <c r="Q74">
-        <v>30.56717463824959</v>
+        <v>30.08737706378082</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1764518799950132</v>
+        <v>0.181290838513347</v>
       </c>
       <c r="T74">
-        <v>3.017364434064969</v>
+        <v>3.129118672363671</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1331823114586445</v>
+        <v>0.1313578962331836</v>
       </c>
       <c r="W74">
-        <v>0.127248836677871</v>
+        <v>0.1275166608329687</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9122076127304419</v>
+        <v>0.899711618035504</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1420356888066708</v>
+        <v>0.1430456888066708</v>
       </c>
       <c r="C75">
-        <v>-91.51986125949338</v>
+        <v>-96.77364167156819</v>
       </c>
       <c r="D75">
-        <v>137.3612123883122</v>
+        <v>135.9345699714128</v>
       </c>
       <c r="E75">
-        <v>244.9672741302637</v>
+        <v>248.7944121254391</v>
       </c>
       <c r="F75">
-        <v>279.3810736478056</v>
+        <v>283.208211642981</v>
       </c>
       <c r="G75">
         <v>50.5</v>
@@ -7419,37 +7419,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M75">
-        <v>41.01314161149786</v>
+        <v>41.57496546918961</v>
       </c>
       <c r="N75">
-        <v>-4.113141611497859</v>
+        <v>-4.674965469189608</v>
       </c>
       <c r="O75">
-        <v>-0.6005186752786874</v>
+        <v>-0.6825449585016827</v>
       </c>
       <c r="P75">
-        <v>-3.512622936219172</v>
+        <v>-3.992420510687926</v>
       </c>
       <c r="Q75">
-        <v>30.08737706378082</v>
+        <v>29.60757948931207</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.181290838513347</v>
+        <v>0.1865020246100142</v>
       </c>
       <c r="T75">
-        <v>3.129118672363671</v>
+        <v>3.249469390531504</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1313578962331836</v>
+        <v>0.1295827895273298</v>
       </c>
       <c r="W75">
-        <v>0.1275166608329687</v>
+        <v>0.127777246497388</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.899711618035504</v>
+        <v>0.8875533529269163</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1430456888066708</v>
+        <v>0.1440556888066708</v>
       </c>
       <c r="C76">
-        <v>-96.77364167156819</v>
+        <v>-101.9980923041957</v>
       </c>
       <c r="D76">
-        <v>135.9345699714128</v>
+        <v>134.5372573339607</v>
       </c>
       <c r="E76">
-        <v>248.7944121254391</v>
+        <v>252.6215501206145</v>
       </c>
       <c r="F76">
-        <v>283.208211642981</v>
+        <v>287.0353496381564</v>
       </c>
       <c r="G76">
         <v>50.5</v>
@@ -7501,37 +7501,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M76">
-        <v>41.57496546918961</v>
+        <v>42.13678932688136</v>
       </c>
       <c r="N76">
-        <v>-4.674965469189608</v>
+        <v>-5.236789326881357</v>
       </c>
       <c r="O76">
-        <v>-0.6825449585016827</v>
+        <v>-0.7645712417246782</v>
       </c>
       <c r="P76">
-        <v>-3.992420510687926</v>
+        <v>-4.47221808515668</v>
       </c>
       <c r="Q76">
-        <v>29.60757948931207</v>
+        <v>29.12778191484331</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1865020246100142</v>
+        <v>0.1921301055944147</v>
       </c>
       <c r="T76">
-        <v>3.249469390531504</v>
+        <v>3.379448166152765</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1295827895273298</v>
+        <v>0.1278550190002987</v>
       </c>
       <c r="W76">
-        <v>0.127777246497388</v>
+        <v>0.1280308832107561</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8875533529269163</v>
+        <v>0.8757193082212241</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1440556888066708</v>
+        <v>0.1450656888066708</v>
       </c>
       <c r="C77">
-        <v>-101.9980923041957</v>
+        <v>-107.1941084237345</v>
       </c>
       <c r="D77">
-        <v>134.5372573339607</v>
+        <v>133.1683792095974</v>
       </c>
       <c r="E77">
-        <v>252.6215501206145</v>
+        <v>256.44868811579</v>
       </c>
       <c r="F77">
-        <v>287.0353496381564</v>
+        <v>290.8624876333319</v>
       </c>
       <c r="G77">
         <v>50.5</v>
@@ -7583,37 +7583,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M77">
-        <v>42.13678932688136</v>
+        <v>42.69861318457312</v>
       </c>
       <c r="N77">
-        <v>-5.236789326881357</v>
+        <v>-5.798613184573114</v>
       </c>
       <c r="O77">
-        <v>-0.7645712417246782</v>
+        <v>-0.8465975249476746</v>
       </c>
       <c r="P77">
-        <v>-4.47221808515668</v>
+        <v>-4.952015659625439</v>
       </c>
       <c r="Q77">
-        <v>29.12778191484331</v>
+        <v>28.64798434037456</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1921301055944147</v>
+        <v>0.1982271933275154</v>
       </c>
       <c r="T77">
-        <v>3.379448166152765</v>
+        <v>3.52025850640913</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1278550190002987</v>
+        <v>0.1261727161187158</v>
       </c>
       <c r="W77">
-        <v>0.1280308832107561</v>
+        <v>0.1282778452737725</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8757193082212241</v>
+        <v>0.8641966857446289</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1450656888066708</v>
+        <v>0.1460756888066708</v>
       </c>
       <c r="C78">
-        <v>-107.1941084237345</v>
+        <v>-112.3625492272207</v>
       </c>
       <c r="D78">
-        <v>133.1683792095974</v>
+        <v>131.8270764012865</v>
       </c>
       <c r="E78">
-        <v>256.44868811579</v>
+        <v>260.2758261109654</v>
       </c>
       <c r="F78">
-        <v>290.8624876333319</v>
+        <v>294.6896256285073</v>
       </c>
       <c r="G78">
         <v>50.5</v>
@@ -7665,37 +7665,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M78">
-        <v>42.69861318457312</v>
+        <v>43.26043704226487</v>
       </c>
       <c r="N78">
-        <v>-5.798613184573114</v>
+        <v>-6.360437042264863</v>
       </c>
       <c r="O78">
-        <v>-0.8465975249476746</v>
+        <v>-0.9286238081706699</v>
       </c>
       <c r="P78">
-        <v>-4.952015659625439</v>
+        <v>-5.431813234094193</v>
       </c>
       <c r="Q78">
-        <v>28.64798434037456</v>
+        <v>28.1681867659058</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1982271933275154</v>
+        <v>0.2048544626026247</v>
       </c>
       <c r="T78">
-        <v>3.52025850640913</v>
+        <v>3.673313224079092</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1261727161187158</v>
+        <v>0.1245341094158754</v>
       </c>
       <c r="W78">
-        <v>0.1282778452737725</v>
+        <v>0.1285183927377495</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8641966857446289</v>
+        <v>0.8529733521635299</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1460756888066708</v>
+        <v>0.1470856888066708</v>
       </c>
       <c r="C79">
-        <v>-112.3625492272207</v>
+        <v>-117.5042396407485</v>
       </c>
       <c r="D79">
-        <v>131.8270764012865</v>
+        <v>130.5125239829342</v>
       </c>
       <c r="E79">
-        <v>260.2758261109654</v>
+        <v>264.1029641061408</v>
       </c>
       <c r="F79">
-        <v>294.6896256285073</v>
+        <v>298.5167636236827</v>
       </c>
       <c r="G79">
         <v>50.5</v>
@@ -7747,37 +7747,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M79">
-        <v>43.26043704226487</v>
+        <v>43.82226089995662</v>
       </c>
       <c r="N79">
-        <v>-6.360437042264863</v>
+        <v>-6.922260899956612</v>
       </c>
       <c r="O79">
-        <v>-0.9286238081706699</v>
+        <v>-1.010650091393665</v>
       </c>
       <c r="P79">
-        <v>-5.431813234094193</v>
+        <v>-5.911610808562947</v>
       </c>
       <c r="Q79">
-        <v>28.1681867659058</v>
+        <v>27.68838919143705</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2048544626026247</v>
+        <v>0.212084210902744</v>
       </c>
       <c r="T79">
-        <v>3.673313224079092</v>
+        <v>3.840282006991779</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1245341094158754</v>
+        <v>0.122937518269518</v>
       </c>
       <c r="W79">
-        <v>0.1285183927377495</v>
+        <v>0.1287527723180348</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8529733521635299</v>
+        <v>0.8420377963665616</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1470856888066708</v>
+        <v>0.1480956888066708</v>
       </c>
       <c r="C80">
-        <v>-117.5042396407485</v>
+        <v>-122.6199720113124</v>
       </c>
       <c r="D80">
-        <v>130.5125239829342</v>
+        <v>129.2239296075457</v>
       </c>
       <c r="E80">
-        <v>264.1029641061408</v>
+        <v>267.9301021013162</v>
       </c>
       <c r="F80">
-        <v>298.5167636236827</v>
+        <v>302.3439016188581</v>
       </c>
       <c r="G80">
         <v>50.5</v>
@@ -7829,37 +7829,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M80">
-        <v>43.82226089995662</v>
+        <v>44.38408475764837</v>
       </c>
       <c r="N80">
-        <v>-6.922260899956612</v>
+        <v>-7.484084757648361</v>
       </c>
       <c r="O80">
-        <v>-1.010650091393665</v>
+        <v>-1.092676374616661</v>
       </c>
       <c r="P80">
-        <v>-5.911610808562947</v>
+        <v>-6.391408383031701</v>
       </c>
       <c r="Q80">
-        <v>27.68838919143705</v>
+        <v>27.20859161696829</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.212084210902744</v>
+        <v>0.2200025066600176</v>
       </c>
       <c r="T80">
-        <v>3.840282006991779</v>
+        <v>4.023152578753293</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.122937518269518</v>
+        <v>0.1213813471521823</v>
       </c>
       <c r="W80">
-        <v>0.1287527723180348</v>
+        <v>0.1289812182380597</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8420377963665616</v>
+        <v>0.8313790900834406</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1480956888066708</v>
+        <v>0.1491056888066708</v>
       </c>
       <c r="C81">
-        <v>-122.6199720113124</v>
+        <v>-127.7105076994056</v>
       </c>
       <c r="D81">
-        <v>129.2239296075457</v>
+        <v>127.960531914628</v>
       </c>
       <c r="E81">
-        <v>267.9301021013162</v>
+        <v>271.7572400964917</v>
       </c>
       <c r="F81">
-        <v>302.3439016188581</v>
+        <v>306.1710396140335</v>
       </c>
       <c r="G81">
         <v>50.5</v>
@@ -7911,37 +7911,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M81">
-        <v>44.38408475764837</v>
+        <v>44.94590861534013</v>
       </c>
       <c r="N81">
-        <v>-7.484084757648361</v>
+        <v>-8.045908615340124</v>
       </c>
       <c r="O81">
-        <v>-1.092676374616661</v>
+        <v>-1.174702657839658</v>
       </c>
       <c r="P81">
-        <v>-6.391408383031701</v>
+        <v>-6.871205957500466</v>
       </c>
       <c r="Q81">
-        <v>27.20859161696829</v>
+        <v>26.72879404249953</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2200025066600176</v>
+        <v>0.2287126319930185</v>
       </c>
       <c r="T81">
-        <v>4.023152578753293</v>
+        <v>4.224310207690958</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1213813471521823</v>
+        <v>0.11986408031278</v>
       </c>
       <c r="W81">
-        <v>0.1289812182380597</v>
+        <v>0.1292039530100839</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8313790900834406</v>
+        <v>0.8209868514573975</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1491056888066708</v>
+        <v>0.1501156888066708</v>
       </c>
       <c r="C82">
-        <v>-127.7105076994056</v>
+        <v>-132.7765785790994</v>
       </c>
       <c r="D82">
-        <v>127.960531914628</v>
+        <v>126.7215990301096</v>
       </c>
       <c r="E82">
-        <v>271.7572400964917</v>
+        <v>275.5843780916671</v>
       </c>
       <c r="F82">
-        <v>306.1710396140335</v>
+        <v>309.9981776092089</v>
       </c>
       <c r="G82">
         <v>50.5</v>
@@ -7993,37 +7993,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M82">
-        <v>44.94590861534013</v>
+        <v>45.50773247303188</v>
       </c>
       <c r="N82">
-        <v>-8.045908615340124</v>
+        <v>-8.607732473031874</v>
       </c>
       <c r="O82">
-        <v>-1.174702657839658</v>
+        <v>-1.256728941062653</v>
       </c>
       <c r="P82">
-        <v>-6.871205957500466</v>
+        <v>-7.35100353196922</v>
       </c>
       <c r="Q82">
-        <v>26.72879404249953</v>
+        <v>26.24899646803078</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2287126319930185</v>
+        <v>0.23833961262423</v>
       </c>
       <c r="T82">
-        <v>4.224310207690958</v>
+        <v>4.446642323885218</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.11986408031278</v>
+        <v>0.1183842768521284</v>
       </c>
       <c r="W82">
-        <v>0.1292039530100839</v>
+        <v>0.1294211881581076</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8209868514573975</v>
+        <v>0.8108512113159481</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1501156888066708</v>
+        <v>0.1511256888066708</v>
       </c>
       <c r="C83">
-        <v>-132.7765785790994</v>
+        <v>-137.8188884518149</v>
       </c>
       <c r="D83">
-        <v>126.7215990301096</v>
+        <v>125.5064271525694</v>
       </c>
       <c r="E83">
-        <v>275.5843780916671</v>
+        <v>279.4115160868425</v>
       </c>
       <c r="F83">
-        <v>309.9981776092089</v>
+        <v>313.8253156043843</v>
       </c>
       <c r="G83">
         <v>50.5</v>
@@ -8075,37 +8075,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M83">
-        <v>45.50773247303188</v>
+        <v>46.06955633072363</v>
       </c>
       <c r="N83">
-        <v>-8.607732473031874</v>
+        <v>-9.169556330723623</v>
       </c>
       <c r="O83">
-        <v>-1.256728941062653</v>
+        <v>-1.338755224285649</v>
       </c>
       <c r="P83">
-        <v>-7.35100353196922</v>
+        <v>-7.830801106437974</v>
       </c>
       <c r="Q83">
-        <v>26.24899646803078</v>
+        <v>25.76919889356202</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.23833961262423</v>
+        <v>0.2490362577700206</v>
       </c>
       <c r="T83">
-        <v>4.446642323885218</v>
+        <v>4.693678008545509</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1183842768521284</v>
+        <v>0.1169405661588098</v>
       </c>
       <c r="W83">
-        <v>0.1294211881581076</v>
+        <v>0.1296331248878867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8108512113159481</v>
+        <v>0.8009627819096561</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1511256888066708</v>
+        <v>0.1979991159376503</v>
       </c>
       <c r="C84">
-        <v>-137.8188884518149</v>
+        <v>-180.2987895157032</v>
       </c>
       <c r="D84">
-        <v>125.5064271525694</v>
+        <v>86.85366408385657</v>
       </c>
       <c r="E84">
-        <v>279.4115160868425</v>
+        <v>283.2386540820179</v>
       </c>
       <c r="F84">
-        <v>313.8253156043843</v>
+        <v>317.6524535995598</v>
       </c>
       <c r="G84">
         <v>50.5</v>
@@ -8157,45 +8157,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M84">
-        <v>46.06955633072363</v>
+        <v>63.78461268279161</v>
       </c>
       <c r="N84">
-        <v>-9.169556330723623</v>
+        <v>-26.88461268279161</v>
       </c>
       <c r="O84">
-        <v>-1.338755224285649</v>
+        <v>-3.925153451687574</v>
       </c>
       <c r="P84">
-        <v>-7.830801106437974</v>
+        <v>-22.95945923110403</v>
       </c>
       <c r="Q84">
-        <v>25.76919889356202</v>
+        <v>10.64054076889596</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2490362577700206</v>
+        <v>0.2671291384093134</v>
       </c>
       <c r="T84">
-        <v>4.693678008545509</v>
+        <v>5.111527445942572</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1169405661588098</v>
+        <v>0.08446237694962852</v>
       </c>
       <c r="W84">
-        <v>0.1296331248878867</v>
+        <v>0.1838399547085146</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8009627819096561</v>
+        <v>0.5785094311618392</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1979991159376503</v>
+        <v>0.1995491159376504</v>
       </c>
       <c r="C85">
-        <v>-180.2987895157032</v>
+        <v>-185.0015304599361</v>
       </c>
       <c r="D85">
-        <v>86.85366408385657</v>
+        <v>85.97806113479913</v>
       </c>
       <c r="E85">
-        <v>283.2386540820179</v>
+        <v>287.0657920771934</v>
       </c>
       <c r="F85">
-        <v>317.6524535995598</v>
+        <v>321.4795915947352</v>
       </c>
       <c r="G85">
         <v>50.5</v>
@@ -8239,37 +8239,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M85">
-        <v>63.78461268279161</v>
+        <v>64.55310199222284</v>
       </c>
       <c r="N85">
-        <v>-26.88461268279161</v>
+        <v>-27.65310199222283</v>
       </c>
       <c r="O85">
-        <v>-3.925153451687574</v>
+        <v>-4.037352890864533</v>
       </c>
       <c r="P85">
-        <v>-22.95945923110403</v>
+        <v>-23.6157491013583</v>
       </c>
       <c r="Q85">
-        <v>10.64054076889596</v>
+        <v>9.984250898641697</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2671291384093134</v>
+        <v>0.2809622095598955</v>
       </c>
       <c r="T85">
-        <v>5.111527445942572</v>
+        <v>5.430997911313984</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08446237694962852</v>
+        <v>0.08345687246213293</v>
       </c>
       <c r="W85">
-        <v>0.1838399547085146</v>
+        <v>0.1840418600096037</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5785094311618392</v>
+        <v>0.5716224141241982</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1995491159376504</v>
+        <v>0.2010991159376504</v>
       </c>
       <c r="C86">
-        <v>-185.001530459936</v>
+        <v>-189.6867930745229</v>
       </c>
       <c r="D86">
-        <v>85.97806113479913</v>
+        <v>85.11993651538766</v>
       </c>
       <c r="E86">
-        <v>287.0657920771933</v>
+        <v>290.8929300723687</v>
       </c>
       <c r="F86">
-        <v>321.4795915947352</v>
+        <v>325.3067295899106</v>
       </c>
       <c r="G86">
         <v>50.5</v>
@@ -8321,37 +8321,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M86">
-        <v>64.55310199222282</v>
+        <v>65.32159130165404</v>
       </c>
       <c r="N86">
-        <v>-27.65310199222282</v>
+        <v>-28.42159130165403</v>
       </c>
       <c r="O86">
-        <v>-4.037352890864531</v>
+        <v>-4.149552330041488</v>
       </c>
       <c r="P86">
-        <v>-23.61574910135828</v>
+        <v>-24.27203897161255</v>
       </c>
       <c r="Q86">
-        <v>9.984250898641712</v>
+        <v>9.327961028387449</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2809622095598954</v>
+        <v>0.2966396901972218</v>
       </c>
       <c r="T86">
-        <v>5.43099791131398</v>
+        <v>5.793064438734913</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08345687246213296</v>
+        <v>0.08247502690375492</v>
       </c>
       <c r="W86">
-        <v>0.1840418600096037</v>
+        <v>0.184239014597726</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5716224141241983</v>
+        <v>0.5648974445462667</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2010991159376504</v>
+        <v>0.2026491159376504</v>
       </c>
       <c r="C87">
-        <v>-189.6867930745229</v>
+        <v>-194.3550955277199</v>
       </c>
       <c r="D87">
-        <v>85.11993651538766</v>
+        <v>84.27877205736611</v>
       </c>
       <c r="E87">
-        <v>290.8929300723687</v>
+        <v>294.7200680675442</v>
       </c>
       <c r="F87">
-        <v>325.3067295899106</v>
+        <v>329.133867585086</v>
       </c>
       <c r="G87">
         <v>50.5</v>
@@ -8403,37 +8403,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M87">
-        <v>65.32159130165404</v>
+        <v>66.09008061108527</v>
       </c>
       <c r="N87">
-        <v>-28.42159130165403</v>
+        <v>-29.19008061108526</v>
       </c>
       <c r="O87">
-        <v>-4.149552330041488</v>
+        <v>-4.261751769218448</v>
       </c>
       <c r="P87">
-        <v>-24.27203897161255</v>
+        <v>-24.92832884186681</v>
       </c>
       <c r="Q87">
-        <v>9.327961028387449</v>
+        <v>8.671671158133179</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2966396901972218</v>
+        <v>0.3145568109255947</v>
       </c>
       <c r="T87">
-        <v>5.793064438734913</v>
+        <v>6.206854755787406</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08247502690375492</v>
+        <v>0.08151601496301358</v>
       </c>
       <c r="W87">
-        <v>0.184239014597726</v>
+        <v>0.1844315841954269</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5648974445462667</v>
+        <v>0.5583288696096821</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2026491159376504</v>
+        <v>0.2041991159376504</v>
       </c>
       <c r="C88">
-        <v>-194.3550955277199</v>
+        <v>-199.0069357058313</v>
       </c>
       <c r="D88">
-        <v>84.27877205736611</v>
+        <v>83.45406987443009</v>
       </c>
       <c r="E88">
-        <v>294.7200680675442</v>
+        <v>298.5472060627196</v>
       </c>
       <c r="F88">
-        <v>329.133867585086</v>
+        <v>332.9610055802614</v>
       </c>
       <c r="G88">
         <v>50.5</v>
@@ -8485,37 +8485,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M88">
-        <v>66.09008061108527</v>
+        <v>66.8585699205165</v>
       </c>
       <c r="N88">
-        <v>-29.19008061108526</v>
+        <v>-29.9585699205165</v>
       </c>
       <c r="O88">
-        <v>-4.261751769218448</v>
+        <v>-4.373951208395408</v>
       </c>
       <c r="P88">
-        <v>-24.92832884186681</v>
+        <v>-25.58461871212109</v>
       </c>
       <c r="Q88">
-        <v>8.671671158133179</v>
+        <v>8.015381287878906</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3145568109255947</v>
+        <v>0.3352304117660251</v>
       </c>
       <c r="T88">
-        <v>6.206854755787406</v>
+        <v>6.684305121617207</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08151601496301358</v>
+        <v>0.08057904927378352</v>
       </c>
       <c r="W88">
-        <v>0.1844315841954269</v>
+        <v>0.1846197269058243</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5583288696096821</v>
+        <v>0.5519112963957776</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2041991159376504</v>
+        <v>0.2057491159376504</v>
       </c>
       <c r="C89">
-        <v>-199.0069357058313</v>
+        <v>-203.6427921959298</v>
       </c>
       <c r="D89">
-        <v>83.45406987443009</v>
+        <v>82.64535137950706</v>
       </c>
       <c r="E89">
-        <v>298.5472060627196</v>
+        <v>302.374344057895</v>
       </c>
       <c r="F89">
-        <v>332.9610055802614</v>
+        <v>336.7881435754368</v>
       </c>
       <c r="G89">
         <v>50.5</v>
@@ -8567,37 +8567,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M89">
-        <v>66.8585699205165</v>
+        <v>67.62705922994772</v>
       </c>
       <c r="N89">
-        <v>-29.9585699205165</v>
+        <v>-30.72705922994771</v>
       </c>
       <c r="O89">
-        <v>-4.373951208395408</v>
+        <v>-4.486150647572366</v>
       </c>
       <c r="P89">
-        <v>-25.58461871212109</v>
+        <v>-26.24090858237535</v>
       </c>
       <c r="Q89">
-        <v>8.015381287878906</v>
+        <v>7.359091417624647</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3352304117660251</v>
+        <v>0.3593496127465273</v>
       </c>
       <c r="T89">
-        <v>6.684305121617207</v>
+        <v>7.241330548418643</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08057904927378352</v>
+        <v>0.07966337825930872</v>
       </c>
       <c r="W89">
-        <v>0.1846197269058243</v>
+        <v>0.1848035936455308</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5519112963957776</v>
+        <v>0.5456395771185529</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2057491159376504</v>
+        <v>0.2072991159376504</v>
       </c>
       <c r="C90">
-        <v>-203.6427921959298</v>
+        <v>-208.2631252119851</v>
       </c>
       <c r="D90">
-        <v>82.64535137950706</v>
+        <v>81.85215635862721</v>
       </c>
       <c r="E90">
-        <v>302.374344057895</v>
+        <v>306.2014820530704</v>
       </c>
       <c r="F90">
-        <v>336.7881435754368</v>
+        <v>340.6152815706123</v>
       </c>
       <c r="G90">
         <v>50.5</v>
@@ -8649,37 +8649,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M90">
-        <v>67.62705922994772</v>
+        <v>68.39554853937895</v>
       </c>
       <c r="N90">
-        <v>-30.72705922994771</v>
+        <v>-31.49554853937894</v>
       </c>
       <c r="O90">
-        <v>-4.486150647572366</v>
+        <v>-4.598350086749326</v>
       </c>
       <c r="P90">
-        <v>-26.24090858237535</v>
+        <v>-26.89719845262962</v>
       </c>
       <c r="Q90">
-        <v>7.359091417624647</v>
+        <v>6.702801547370377</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3593496127465273</v>
+        <v>0.3878541229962116</v>
       </c>
       <c r="T90">
-        <v>7.241330548418643</v>
+        <v>7.899633325547611</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07966337825930872</v>
+        <v>0.07876828412156367</v>
       </c>
       <c r="W90">
-        <v>0.1848035936455308</v>
+        <v>0.18498332854839</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5456395771185529</v>
+        <v>0.5395087953531759</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2072991159376504</v>
+        <v>0.2088491159376504</v>
       </c>
       <c r="C91">
-        <v>-208.2631252119851</v>
+        <v>-212.8683774681687</v>
       </c>
       <c r="D91">
-        <v>81.85215635862721</v>
+        <v>81.07404209761899</v>
       </c>
       <c r="E91">
-        <v>306.2014820530704</v>
+        <v>310.0286200482458</v>
       </c>
       <c r="F91">
-        <v>340.6152815706123</v>
+        <v>344.4424195657877</v>
       </c>
       <c r="G91">
         <v>50.5</v>
@@ -8731,37 +8731,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M91">
-        <v>68.39554853937895</v>
+        <v>69.16403784881017</v>
       </c>
       <c r="N91">
-        <v>-31.49554853937894</v>
+        <v>-32.26403784881016</v>
       </c>
       <c r="O91">
-        <v>-4.598350086749326</v>
+        <v>-4.710549525926283</v>
       </c>
       <c r="P91">
-        <v>-26.89719845262962</v>
+        <v>-27.55348832288388</v>
       </c>
       <c r="Q91">
-        <v>6.702801547370377</v>
+        <v>6.046511677116115</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3878541229962116</v>
+        <v>0.4220595352958328</v>
       </c>
       <c r="T91">
-        <v>7.899633325547611</v>
+        <v>8.689596658102372</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07876828412156367</v>
+        <v>0.07789308096465741</v>
       </c>
       <c r="W91">
-        <v>0.18498332854839</v>
+        <v>0.1851590693422968</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5395087953531759</v>
+        <v>0.5335142531825852</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2088491159376504</v>
+        <v>0.2103991159376504</v>
       </c>
       <c r="C92">
-        <v>-212.8683774681687</v>
+        <v>-217.4589750028164</v>
       </c>
       <c r="D92">
-        <v>81.07404209761899</v>
+        <v>80.31058255814669</v>
       </c>
       <c r="E92">
-        <v>310.0286200482458</v>
+        <v>313.8557580434212</v>
       </c>
       <c r="F92">
-        <v>344.4424195657877</v>
+        <v>348.2695575609631</v>
       </c>
       <c r="G92">
         <v>50.5</v>
@@ -8813,37 +8813,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M92">
-        <v>69.16403784881017</v>
+        <v>69.9325271582414</v>
       </c>
       <c r="N92">
-        <v>-32.26403784881016</v>
+        <v>-33.03252715824139</v>
       </c>
       <c r="O92">
-        <v>-4.710549525926283</v>
+        <v>-4.822748965103243</v>
       </c>
       <c r="P92">
-        <v>-27.55348832288388</v>
+        <v>-28.20977819313815</v>
       </c>
       <c r="Q92">
-        <v>6.046511677116115</v>
+        <v>5.390221806861845</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4220595352958328</v>
+        <v>0.4638661503287031</v>
       </c>
       <c r="T92">
-        <v>8.689596658102372</v>
+        <v>9.655107397891525</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07789308096465741</v>
+        <v>0.07703711304196888</v>
       </c>
       <c r="W92">
-        <v>0.1851590693422968</v>
+        <v>0.1853309477011726</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5335142531825852</v>
+        <v>0.5276514591915676</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2103991159376504</v>
+        <v>0.2119491159376504</v>
       </c>
       <c r="C93">
-        <v>-217.4589750028164</v>
+        <v>-222.0353279562697</v>
       </c>
       <c r="D93">
-        <v>80.31058255814669</v>
+        <v>79.56136759986879</v>
       </c>
       <c r="E93">
-        <v>313.8557580434212</v>
+        <v>317.6828960385967</v>
       </c>
       <c r="F93">
-        <v>348.2695575609631</v>
+        <v>352.0966955561385</v>
       </c>
       <c r="G93">
         <v>50.5</v>
@@ -8895,37 +8895,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M93">
-        <v>69.9325271582414</v>
+        <v>70.70101646767262</v>
       </c>
       <c r="N93">
-        <v>-33.03252715824139</v>
+        <v>-33.80101646767261</v>
       </c>
       <c r="O93">
-        <v>-4.822748965103243</v>
+        <v>-4.934948404280201</v>
       </c>
       <c r="P93">
-        <v>-28.20977819313815</v>
+        <v>-28.86606806339241</v>
       </c>
       <c r="Q93">
-        <v>5.390221806861845</v>
+        <v>4.733931936607583</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4638661503287031</v>
+        <v>0.5161244191197911</v>
       </c>
       <c r="T93">
-        <v>9.655107397891525</v>
+        <v>10.86199582262797</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07703711304196888</v>
+        <v>0.07619975311759965</v>
       </c>
       <c r="W93">
-        <v>0.1853309477011726</v>
+        <v>0.185499089573986</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5276514591915676</v>
+        <v>0.5219161172438332</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2119491159376504</v>
+        <v>0.2134991159376504</v>
       </c>
       <c r="C94">
-        <v>-222.0353279562697</v>
+        <v>-226.5978313055812</v>
       </c>
       <c r="D94">
-        <v>79.56136759986879</v>
+        <v>78.82600224573275</v>
       </c>
       <c r="E94">
-        <v>317.6828960385967</v>
+        <v>321.5100340337721</v>
       </c>
       <c r="F94">
-        <v>352.0966955561385</v>
+        <v>355.923833551314</v>
       </c>
       <c r="G94">
         <v>50.5</v>
@@ -8977,37 +8977,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M94">
-        <v>70.70101646767262</v>
+        <v>71.46950577710385</v>
       </c>
       <c r="N94">
-        <v>-33.80101646767261</v>
+        <v>-34.56950577710384</v>
       </c>
       <c r="O94">
-        <v>-4.934948404280201</v>
+        <v>-5.047147843457161</v>
       </c>
       <c r="P94">
-        <v>-28.86606806339241</v>
+        <v>-29.52235793364668</v>
       </c>
       <c r="Q94">
-        <v>4.733931936607583</v>
+        <v>4.077642066353313</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5161244191197911</v>
+        <v>0.5833136218511898</v>
       </c>
       <c r="T94">
-        <v>10.86199582262797</v>
+        <v>12.41370951157482</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07619975311759965</v>
+        <v>0.07538040093353944</v>
       </c>
       <c r="W94">
-        <v>0.185499089573986</v>
+        <v>0.1856636154925453</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5219161172438332</v>
+        <v>0.5163041159831467</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2134991159376504</v>
+        <v>0.2150491159376504</v>
       </c>
       <c r="C95">
-        <v>-226.5978313055812</v>
+        <v>-231.1468655588493</v>
       </c>
       <c r="D95">
-        <v>78.82600224573275</v>
+        <v>78.10410598764007</v>
       </c>
       <c r="E95">
-        <v>321.5100340337721</v>
+        <v>325.3371720289475</v>
       </c>
       <c r="F95">
-        <v>355.923833551314</v>
+        <v>359.7509715464894</v>
       </c>
       <c r="G95">
         <v>50.5</v>
@@ -9059,37 +9059,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M95">
-        <v>71.46950577710385</v>
+        <v>72.23799508653507</v>
       </c>
       <c r="N95">
-        <v>-34.56950577710384</v>
+        <v>-35.33799508653506</v>
       </c>
       <c r="O95">
-        <v>-5.047147843457161</v>
+        <v>-5.159347282634118</v>
       </c>
       <c r="P95">
-        <v>-29.52235793364668</v>
+        <v>-30.17864780390094</v>
       </c>
       <c r="Q95">
-        <v>4.077642066353313</v>
+        <v>3.421352196099054</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5833136218511898</v>
+        <v>0.672899225493055</v>
       </c>
       <c r="T95">
-        <v>12.41370951157482</v>
+        <v>14.4826610968373</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07538040093353944</v>
+        <v>0.074578481774672</v>
       </c>
       <c r="W95">
-        <v>0.1856636154925453</v>
+        <v>0.1858246408596459</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5163041159831467</v>
+        <v>0.5108115190046028</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2150491159376504</v>
+        <v>0.2165991159376504</v>
       </c>
       <c r="C96">
-        <v>-231.1468655588493</v>
+        <v>-235.6827974117461</v>
       </c>
       <c r="D96">
-        <v>78.10410598764007</v>
+        <v>77.39531212991872</v>
       </c>
       <c r="E96">
-        <v>325.3371720289475</v>
+        <v>329.1643100241229</v>
       </c>
       <c r="F96">
-        <v>359.7509715464894</v>
+        <v>363.5781095416648</v>
       </c>
       <c r="G96">
         <v>50.5</v>
@@ -9141,37 +9141,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M96">
-        <v>72.23799508653507</v>
+        <v>73.0064843959663</v>
       </c>
       <c r="N96">
-        <v>-35.33799508653506</v>
+        <v>-36.10648439596629</v>
       </c>
       <c r="O96">
-        <v>-5.159347282634118</v>
+        <v>-5.271546721811078</v>
       </c>
       <c r="P96">
-        <v>-30.17864780390094</v>
+        <v>-30.83493767415521</v>
       </c>
       <c r="Q96">
-        <v>3.421352196099054</v>
+        <v>2.765062325844781</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.672899225493055</v>
+        <v>0.7983190705916663</v>
       </c>
       <c r="T96">
-        <v>14.4826610968373</v>
+        <v>17.37919331620476</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.074578481774672</v>
+        <v>0.07379344512441229</v>
       </c>
       <c r="W96">
-        <v>0.1858246408596459</v>
+        <v>0.185982276219018</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5108115190046028</v>
+        <v>0.5054345556466595</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2165991159376504</v>
+        <v>0.2181491159376504</v>
       </c>
       <c r="C97">
-        <v>-235.6827974117461</v>
+        <v>-240.2059803686188</v>
       </c>
       <c r="D97">
-        <v>77.39531212991872</v>
+        <v>76.69926716822148</v>
       </c>
       <c r="E97">
-        <v>329.1643100241229</v>
+        <v>332.9914480192984</v>
       </c>
       <c r="F97">
-        <v>363.5781095416648</v>
+        <v>367.4052475368402</v>
       </c>
       <c r="G97">
         <v>50.5</v>
@@ -9223,37 +9223,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M97">
-        <v>73.0064843959663</v>
+        <v>73.77497370539753</v>
       </c>
       <c r="N97">
-        <v>-36.10648439596629</v>
+        <v>-36.87497370539752</v>
       </c>
       <c r="O97">
-        <v>-5.271546721811078</v>
+        <v>-5.383746160988038</v>
       </c>
       <c r="P97">
-        <v>-30.83493767415521</v>
+        <v>-31.49122754440948</v>
       </c>
       <c r="Q97">
-        <v>2.765062325844781</v>
+        <v>2.108772455590511</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7983190705916663</v>
+        <v>0.9864488382395833</v>
       </c>
       <c r="T97">
-        <v>17.37919331620476</v>
+        <v>21.72399164525596</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07379344512441229</v>
+        <v>0.07302476340436631</v>
       </c>
       <c r="W97">
-        <v>0.185982276219018</v>
+        <v>0.1861366275084032</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5054345556466595</v>
+        <v>0.5001696123586734</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2181491159376504</v>
+        <v>0.2540701513882027</v>
       </c>
       <c r="C98">
-        <v>-240.2059803686187</v>
+        <v>-257.2616922934577</v>
       </c>
       <c r="D98">
-        <v>76.69926716822152</v>
+        <v>63.4706932385579</v>
       </c>
       <c r="E98">
-        <v>332.9914480192983</v>
+        <v>336.8185860144737</v>
       </c>
       <c r="F98">
-        <v>367.4052475368402</v>
+        <v>371.2323855320156</v>
       </c>
       <c r="G98">
         <v>50.5</v>
@@ -9305,45 +9305,45 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M98">
-        <v>73.77497370539751</v>
+        <v>87.53659650844928</v>
       </c>
       <c r="N98">
-        <v>-36.87497370539751</v>
+        <v>-50.63659650844927</v>
       </c>
       <c r="O98">
-        <v>-5.383746160988036</v>
+        <v>-7.392943090233594</v>
       </c>
       <c r="P98">
-        <v>-31.49122754440947</v>
+        <v>-43.24365341821568</v>
       </c>
       <c r="Q98">
-        <v>2.108772455590522</v>
+        <v>-9.643653418215685</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9864488382395807</v>
+        <v>1.314032966004519</v>
       </c>
       <c r="T98">
-        <v>21.7239916452559</v>
+        <v>29.28944494236765</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07302476340436632</v>
+        <v>0.06154454496617302</v>
       </c>
       <c r="W98">
-        <v>0.1861366275084032</v>
+        <v>0.2212877962969764</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5001696123586735</v>
+        <v>0.4215379792203632</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2540701513882027</v>
+        <v>0.2559701513882027</v>
       </c>
       <c r="C99">
-        <v>-257.2616922934577</v>
+        <v>-261.662624028404</v>
       </c>
       <c r="D99">
-        <v>63.4706932385579</v>
+        <v>62.89689949878696</v>
       </c>
       <c r="E99">
-        <v>336.8185860144737</v>
+        <v>340.6457240096491</v>
       </c>
       <c r="F99">
-        <v>371.2323855320156</v>
+        <v>375.059523527191</v>
       </c>
       <c r="G99">
         <v>50.5</v>
@@ -9387,37 +9387,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M99">
-        <v>87.53659650844928</v>
+        <v>88.43903564771165</v>
       </c>
       <c r="N99">
-        <v>-50.63659650844927</v>
+        <v>-51.53903564771164</v>
       </c>
       <c r="O99">
-        <v>-7.392943090233594</v>
+        <v>-7.524699204565899</v>
       </c>
       <c r="P99">
-        <v>-43.24365341821568</v>
+        <v>-44.01433644314574</v>
       </c>
       <c r="Q99">
-        <v>-9.643653418215685</v>
+        <v>-10.41433644314575</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.314032966004519</v>
+        <v>1.948149449006779</v>
       </c>
       <c r="T99">
-        <v>29.28944494236765</v>
+        <v>43.93416741355146</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06154454496617302</v>
+        <v>0.0609165394052937</v>
       </c>
       <c r="W99">
-        <v>0.2212877962969764</v>
+        <v>0.2214358800082318</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4215379792203632</v>
+        <v>0.4172365712691349</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2559701513882027</v>
+        <v>0.2578701513882027</v>
       </c>
       <c r="C100">
-        <v>-261.662624028404</v>
+        <v>-266.0532741834259</v>
       </c>
       <c r="D100">
-        <v>62.89689949878696</v>
+        <v>62.33338733894065</v>
       </c>
       <c r="E100">
-        <v>340.6457240096491</v>
+        <v>344.4728620048246</v>
       </c>
       <c r="F100">
-        <v>375.059523527191</v>
+        <v>378.8866615223665</v>
       </c>
       <c r="G100">
         <v>50.5</v>
@@ -9469,37 +9469,37 @@
         <v>36.90000000000001</v>
       </c>
       <c r="M100">
-        <v>88.43903564771165</v>
+        <v>89.34147478697402</v>
       </c>
       <c r="N100">
-        <v>-51.53903564771164</v>
+        <v>-52.44147478697401</v>
       </c>
       <c r="O100">
-        <v>-7.524699204565899</v>
+        <v>-7.656455318898205</v>
       </c>
       <c r="P100">
-        <v>-44.01433644314574</v>
+        <v>-44.78501946807581</v>
       </c>
       <c r="Q100">
-        <v>-10.41433644314575</v>
+        <v>-11.18501946807582</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.948149449006779</v>
+        <v>3.850498898013558</v>
       </c>
       <c r="T100">
-        <v>43.93416741355146</v>
+        <v>87.86833482710294</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0609165394052937</v>
+        <v>0.06030122082544224</v>
       </c>
       <c r="W100">
-        <v>0.2214358800082318</v>
+        <v>0.2215809721293607</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4172365712691349</v>
+        <v>0.4130220604482345</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2578701513882027</v>
-      </c>
-      <c r="C101">
-        <v>-266.0532741834259</v>
-      </c>
-      <c r="D101">
-        <v>62.33338733894065</v>
-      </c>
-      <c r="E101">
-        <v>344.4728620048246</v>
-      </c>
-      <c r="F101">
-        <v>378.8866615223665</v>
-      </c>
-      <c r="G101">
-        <v>50.5</v>
-      </c>
-      <c r="H101">
-        <v>348.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>70.5</v>
-      </c>
-      <c r="K101">
-        <v>33.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>36.90000000000001</v>
-      </c>
-      <c r="M101">
-        <v>89.34147478697402</v>
-      </c>
-      <c r="N101">
-        <v>-52.44147478697401</v>
-      </c>
-      <c r="O101">
-        <v>-7.656455318898205</v>
-      </c>
-      <c r="P101">
-        <v>-44.78501946807581</v>
-      </c>
-      <c r="Q101">
-        <v>-11.18501946807582</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.850498898013558</v>
-      </c>
-      <c r="T101">
-        <v>87.86833482710294</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06030122082544224</v>
-      </c>
-      <c r="W101">
-        <v>0.2215809721293607</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4130220604482345</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
